--- a/VanHanhCD1/wwwroot/templates/BMVH_ThieuKet1.xlsx
+++ b/VanHanhCD1/wwwroot/templates/BMVH_ThieuKet1.xlsx
@@ -5,28 +5,37 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03. Project Hoa Phat\07. Backend\VanHanhCD1_API-main\VanHanhCD1\wwwroot\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC066C2-5681-4F18-A3F2-D4F0073EF99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52DA22B-B95B-4016-8C42-83E91663E1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="148">
   <si>
     <t>BM.09/QT.05.03</t>
   </si>
@@ -499,6 +508,30 @@
   </si>
   <si>
     <t>NHẬT KÝ VẬN HÀNH THIÊU KẾT 1</t>
+  </si>
+  <si>
+    <t>Độ dày lớp liệu</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>LI601aAM</t>
+  </si>
+  <si>
+    <t>LI601bAM</t>
+  </si>
+  <si>
+    <t>LI601cAM</t>
+  </si>
+  <si>
+    <t>LI601dAM</t>
+  </si>
+  <si>
+    <t>LI601eaAM</t>
+  </si>
+  <si>
+    <t>LI601eAM</t>
   </si>
 </sst>
 </file>
@@ -702,7 +735,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="56">
+  <borders count="61">
     <border>
       <left/>
       <right/>
@@ -1407,11 +1440,72 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1508,9 +1602,6 @@
     <xf numFmtId="1" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1548,33 +1639,222 @@
     <xf numFmtId="164" fontId="28" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1638,206 +1918,23 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1857,23 +1954,49 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1922,8 +2045,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1903879" y="133350"/>
-          <a:ext cx="2086995" cy="843803"/>
+          <a:off x="1902279" y="133350"/>
+          <a:ext cx="2079790" cy="851807"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="2095500" cy="857251"/>
         </a:xfrm>
@@ -2628,7 +2751,11 @@
     <col min="31" max="31" width="7.625" customWidth="1"/>
     <col min="32" max="52" width="6.75" customWidth="1"/>
     <col min="53" max="55" width="7.625" customWidth="1"/>
-    <col min="58" max="58" width="33.125" style="40" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="10" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="10" style="39" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="10" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:63" ht="18.75" customHeight="1">
@@ -2672,51 +2799,51 @@
       <c r="D2" s="1"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="50" t="s">
+      <c r="G2" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="50"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="50"/>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="50"/>
-      <c r="AA2" s="50"/>
-      <c r="AB2" s="50"/>
-      <c r="AC2" s="50"/>
-      <c r="AD2" s="50"/>
-      <c r="AE2" s="50"/>
-      <c r="AF2" s="50"/>
-      <c r="AG2" s="50"/>
-      <c r="AH2" s="50"/>
-      <c r="AI2" s="50"/>
-      <c r="AJ2" s="50"/>
-      <c r="AK2" s="50"/>
-      <c r="AL2" s="50"/>
-      <c r="AM2" s="50"/>
-      <c r="AN2" s="50"/>
-      <c r="AO2" s="50"/>
-      <c r="AP2" s="50"/>
-      <c r="AQ2" s="50"/>
-      <c r="AR2" s="50"/>
-      <c r="AS2" s="50"/>
-      <c r="AT2" s="50"/>
-      <c r="AU2" s="50"/>
-      <c r="AV2" s="50"/>
-      <c r="AW2" s="50"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
+      <c r="O2" s="118"/>
+      <c r="P2" s="118"/>
+      <c r="Q2" s="118"/>
+      <c r="R2" s="118"/>
+      <c r="S2" s="118"/>
+      <c r="T2" s="118"/>
+      <c r="U2" s="118"/>
+      <c r="V2" s="118"/>
+      <c r="W2" s="118"/>
+      <c r="X2" s="118"/>
+      <c r="Y2" s="118"/>
+      <c r="Z2" s="118"/>
+      <c r="AA2" s="118"/>
+      <c r="AB2" s="118"/>
+      <c r="AC2" s="118"/>
+      <c r="AD2" s="118"/>
+      <c r="AE2" s="118"/>
+      <c r="AF2" s="118"/>
+      <c r="AG2" s="118"/>
+      <c r="AH2" s="118"/>
+      <c r="AI2" s="118"/>
+      <c r="AJ2" s="118"/>
+      <c r="AK2" s="118"/>
+      <c r="AL2" s="118"/>
+      <c r="AM2" s="118"/>
+      <c r="AN2" s="118"/>
+      <c r="AO2" s="118"/>
+      <c r="AP2" s="118"/>
+      <c r="AQ2" s="118"/>
+      <c r="AR2" s="118"/>
+      <c r="AS2" s="118"/>
+      <c r="AT2" s="118"/>
+      <c r="AU2" s="118"/>
+      <c r="AV2" s="118"/>
+      <c r="AW2" s="118"/>
       <c r="BC2" s="6" t="s">
         <v>2</v>
       </c>
@@ -2727,49 +2854,49 @@
       <c r="D3" s="1"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="50"/>
-      <c r="U3" s="50"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
-      <c r="AB3" s="50"/>
-      <c r="AC3" s="50"/>
-      <c r="AD3" s="50"/>
-      <c r="AE3" s="50"/>
-      <c r="AF3" s="50"/>
-      <c r="AG3" s="50"/>
-      <c r="AH3" s="50"/>
-      <c r="AI3" s="50"/>
-      <c r="AJ3" s="50"/>
-      <c r="AK3" s="50"/>
-      <c r="AL3" s="50"/>
-      <c r="AM3" s="50"/>
-      <c r="AN3" s="50"/>
-      <c r="AO3" s="50"/>
-      <c r="AP3" s="50"/>
-      <c r="AQ3" s="50"/>
-      <c r="AR3" s="50"/>
-      <c r="AS3" s="50"/>
-      <c r="AT3" s="50"/>
-      <c r="AU3" s="50"/>
-      <c r="AV3" s="50"/>
-      <c r="AW3" s="50"/>
+      <c r="G3" s="118"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="118"/>
+      <c r="K3" s="118"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="N3" s="118"/>
+      <c r="O3" s="118"/>
+      <c r="P3" s="118"/>
+      <c r="Q3" s="118"/>
+      <c r="R3" s="118"/>
+      <c r="S3" s="118"/>
+      <c r="T3" s="118"/>
+      <c r="U3" s="118"/>
+      <c r="V3" s="118"/>
+      <c r="W3" s="118"/>
+      <c r="X3" s="118"/>
+      <c r="Y3" s="118"/>
+      <c r="Z3" s="118"/>
+      <c r="AA3" s="118"/>
+      <c r="AB3" s="118"/>
+      <c r="AC3" s="118"/>
+      <c r="AD3" s="118"/>
+      <c r="AE3" s="118"/>
+      <c r="AF3" s="118"/>
+      <c r="AG3" s="118"/>
+      <c r="AH3" s="118"/>
+      <c r="AI3" s="118"/>
+      <c r="AJ3" s="118"/>
+      <c r="AK3" s="118"/>
+      <c r="AL3" s="118"/>
+      <c r="AM3" s="118"/>
+      <c r="AN3" s="118"/>
+      <c r="AO3" s="118"/>
+      <c r="AP3" s="118"/>
+      <c r="AQ3" s="118"/>
+      <c r="AR3" s="118"/>
+      <c r="AS3" s="118"/>
+      <c r="AT3" s="118"/>
+      <c r="AU3" s="118"/>
+      <c r="AV3" s="118"/>
+      <c r="AW3" s="118"/>
     </row>
     <row r="4" spans="1:63" ht="29.25" customHeight="1">
       <c r="B4" s="4"/>
@@ -2820,258 +2947,278 @@
       <c r="AC5" s="8"/>
       <c r="AD5" s="8"/>
       <c r="AE5" s="8"/>
-      <c r="BF5" s="40"/>
+      <c r="BF5" s="39"/>
     </row>
     <row r="6" spans="1:63" s="10" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="61" t="s">
+      <c r="B6" s="127"/>
+      <c r="C6" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="134" t="s">
+      <c r="D6" s="72" t="s">
         <v>5</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="139" t="s">
+      <c r="F6" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="89"/>
-      <c r="H6" s="139" t="s">
+      <c r="G6" s="78"/>
+      <c r="H6" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="88"/>
-      <c r="O6" s="88"/>
-      <c r="P6" s="88"/>
-      <c r="Q6" s="88"/>
-      <c r="R6" s="88"/>
-      <c r="S6" s="88"/>
-      <c r="T6" s="88"/>
-      <c r="U6" s="88"/>
-      <c r="V6" s="88"/>
-      <c r="W6" s="88"/>
-      <c r="X6" s="88"/>
-      <c r="Y6" s="88"/>
-      <c r="Z6" s="88"/>
-      <c r="AA6" s="88"/>
-      <c r="AB6" s="88"/>
-      <c r="AC6" s="88"/>
-      <c r="AD6" s="88"/>
-      <c r="AE6" s="88"/>
-      <c r="AF6" s="88"/>
-      <c r="AG6" s="88"/>
-      <c r="AH6" s="88"/>
-      <c r="AI6" s="88"/>
-      <c r="AJ6" s="88"/>
-      <c r="AK6" s="88"/>
-      <c r="AL6" s="88"/>
-      <c r="AM6" s="88"/>
-      <c r="AN6" s="88"/>
-      <c r="AO6" s="88"/>
-      <c r="AP6" s="88"/>
-      <c r="AQ6" s="88"/>
-      <c r="AR6" s="88"/>
-      <c r="AS6" s="88"/>
-      <c r="AT6" s="88"/>
-      <c r="AU6" s="88"/>
-      <c r="AV6" s="88"/>
-      <c r="AW6" s="88"/>
-      <c r="AX6" s="88"/>
-      <c r="AY6" s="88"/>
-      <c r="AZ6" s="88"/>
-      <c r="BA6" s="88"/>
-      <c r="BB6" s="88"/>
-      <c r="BC6" s="89"/>
-      <c r="BD6" s="9"/>
-      <c r="BE6" s="9"/>
-      <c r="BF6" s="40"/>
-      <c r="BG6" s="9"/>
-      <c r="BH6" s="9"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="77"/>
+      <c r="N6" s="77"/>
+      <c r="O6" s="77"/>
+      <c r="P6" s="77"/>
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="77"/>
+      <c r="T6" s="77"/>
+      <c r="U6" s="77"/>
+      <c r="V6" s="77"/>
+      <c r="W6" s="77"/>
+      <c r="X6" s="77"/>
+      <c r="Y6" s="77"/>
+      <c r="Z6" s="77"/>
+      <c r="AA6" s="77"/>
+      <c r="AB6" s="77"/>
+      <c r="AC6" s="77"/>
+      <c r="AD6" s="77"/>
+      <c r="AE6" s="77"/>
+      <c r="AF6" s="77"/>
+      <c r="AG6" s="77"/>
+      <c r="AH6" s="77"/>
+      <c r="AI6" s="77"/>
+      <c r="AJ6" s="77"/>
+      <c r="AK6" s="77"/>
+      <c r="AL6" s="77"/>
+      <c r="AM6" s="77"/>
+      <c r="AN6" s="77"/>
+      <c r="AO6" s="77"/>
+      <c r="AP6" s="77"/>
+      <c r="AQ6" s="77"/>
+      <c r="AR6" s="77"/>
+      <c r="AS6" s="77"/>
+      <c r="AT6" s="77"/>
+      <c r="AU6" s="77"/>
+      <c r="AV6" s="77"/>
+      <c r="AW6" s="77"/>
+      <c r="AX6" s="77"/>
+      <c r="AY6" s="77"/>
+      <c r="AZ6" s="77"/>
+      <c r="BA6" s="77"/>
+      <c r="BB6" s="77"/>
+      <c r="BC6" s="77"/>
+      <c r="BD6" s="76"/>
+      <c r="BE6" s="77"/>
+      <c r="BF6" s="77"/>
+      <c r="BG6" s="77"/>
+      <c r="BH6" s="162"/>
       <c r="BI6" s="9"/>
       <c r="BJ6" s="9"/>
       <c r="BK6" s="9"/>
     </row>
-    <row r="7" spans="1:63" s="10" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A7" s="66"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="135"/>
-      <c r="E7" s="134" t="s">
+    <row r="7" spans="1:63" s="10" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
+      <c r="A7" s="128"/>
+      <c r="B7" s="129"/>
+      <c r="C7" s="124"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="140" t="s">
+      <c r="F7" s="79" t="s">
         <v>122</v>
       </c>
-      <c r="G7" s="142" t="s">
+      <c r="G7" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="137" t="s">
+      <c r="H7" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="52"/>
-      <c r="J7" s="137" t="s">
+      <c r="I7" s="50"/>
+      <c r="J7" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="52"/>
-      <c r="L7" s="137" t="s">
+      <c r="K7" s="50"/>
+      <c r="L7" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="52"/>
-      <c r="N7" s="137" t="s">
+      <c r="M7" s="50"/>
+      <c r="N7" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="O7" s="52"/>
-      <c r="P7" s="137" t="s">
+      <c r="O7" s="50"/>
+      <c r="P7" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="51" t="s">
+      <c r="Q7" s="50"/>
+      <c r="R7" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="S7" s="59"/>
-      <c r="T7" s="74" t="s">
+      <c r="S7" s="121"/>
+      <c r="T7" s="136" t="s">
         <v>18</v>
       </c>
-      <c r="U7" s="75"/>
-      <c r="V7" s="74" t="s">
+      <c r="U7" s="137"/>
+      <c r="V7" s="136" t="s">
         <v>19</v>
       </c>
-      <c r="W7" s="75"/>
-      <c r="X7" s="74" t="s">
+      <c r="W7" s="137"/>
+      <c r="X7" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="Y7" s="75"/>
-      <c r="Z7" s="74" t="s">
+      <c r="Y7" s="137"/>
+      <c r="Z7" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="AA7" s="75"/>
-      <c r="AB7" s="78" t="s">
+      <c r="AA7" s="137"/>
+      <c r="AB7" s="140" t="s">
         <v>22</v>
       </c>
-      <c r="AC7" s="75"/>
-      <c r="AD7" s="74" t="s">
+      <c r="AC7" s="137"/>
+      <c r="AD7" s="136" t="s">
         <v>23</v>
       </c>
-      <c r="AE7" s="75"/>
-      <c r="AF7" s="51" t="s">
+      <c r="AE7" s="137"/>
+      <c r="AF7" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="AG7" s="52"/>
-      <c r="AH7" s="55" t="s">
+      <c r="AG7" s="50"/>
+      <c r="AH7" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="AI7" s="52"/>
-      <c r="AJ7" s="55" t="s">
+      <c r="AI7" s="50"/>
+      <c r="AJ7" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="AK7" s="52"/>
-      <c r="AL7" s="55" t="s">
+      <c r="AK7" s="50"/>
+      <c r="AL7" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="AM7" s="52"/>
-      <c r="AN7" s="55" t="s">
+      <c r="AM7" s="50"/>
+      <c r="AN7" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="AO7" s="52"/>
-      <c r="AP7" s="55" t="s">
+      <c r="AO7" s="50"/>
+      <c r="AP7" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="AQ7" s="52"/>
-      <c r="AR7" s="55" t="s">
+      <c r="AQ7" s="50"/>
+      <c r="AR7" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="AS7" s="52"/>
-      <c r="AT7" s="55" t="s">
+      <c r="AS7" s="50"/>
+      <c r="AT7" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="AU7" s="52"/>
-      <c r="AV7" s="55" t="s">
+      <c r="AU7" s="50"/>
+      <c r="AV7" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="AW7" s="52"/>
-      <c r="AX7" s="55" t="s">
+      <c r="AW7" s="50"/>
+      <c r="AX7" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="AY7" s="52"/>
-      <c r="AZ7" s="55" t="s">
+      <c r="AY7" s="50"/>
+      <c r="AZ7" s="49" t="s">
         <v>123</v>
       </c>
-      <c r="BA7" s="52"/>
-      <c r="BB7" s="137" t="s">
+      <c r="BA7" s="50"/>
+      <c r="BB7" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="BC7" s="52"/>
-      <c r="BF7" s="40"/>
+      <c r="BC7" s="50"/>
+      <c r="BD7" s="76" t="s">
+        <v>140</v>
+      </c>
+      <c r="BE7" s="77"/>
+      <c r="BF7" s="77"/>
+      <c r="BG7" s="77"/>
+      <c r="BH7" s="162"/>
     </row>
     <row r="8" spans="1:63" s="10" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
-      <c r="A8" s="66"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="136"/>
-      <c r="F8" s="141"/>
-      <c r="G8" s="143"/>
-      <c r="H8" s="138"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="138"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="138"/>
-      <c r="M8" s="54"/>
-      <c r="N8" s="138"/>
-      <c r="O8" s="54"/>
-      <c r="P8" s="138"/>
-      <c r="Q8" s="54"/>
-      <c r="R8" s="53"/>
-      <c r="S8" s="60"/>
-      <c r="T8" s="76"/>
-      <c r="U8" s="77"/>
-      <c r="V8" s="76"/>
-      <c r="W8" s="77"/>
-      <c r="X8" s="76"/>
-      <c r="Y8" s="77"/>
-      <c r="Z8" s="76"/>
-      <c r="AA8" s="77"/>
-      <c r="AB8" s="79"/>
-      <c r="AC8" s="77"/>
-      <c r="AD8" s="76"/>
-      <c r="AE8" s="77"/>
-      <c r="AF8" s="53"/>
-      <c r="AG8" s="54"/>
-      <c r="AH8" s="56"/>
-      <c r="AI8" s="54"/>
-      <c r="AJ8" s="56"/>
-      <c r="AK8" s="54"/>
-      <c r="AL8" s="56"/>
-      <c r="AM8" s="54"/>
-      <c r="AN8" s="56"/>
-      <c r="AO8" s="54"/>
-      <c r="AP8" s="144"/>
-      <c r="AQ8" s="145"/>
-      <c r="AR8" s="144"/>
-      <c r="AS8" s="145"/>
-      <c r="AT8" s="144"/>
-      <c r="AU8" s="145"/>
-      <c r="AV8" s="144"/>
-      <c r="AW8" s="145"/>
-      <c r="AX8" s="144"/>
-      <c r="AY8" s="145"/>
-      <c r="AZ8" s="144"/>
-      <c r="BA8" s="145"/>
-      <c r="BB8" s="146"/>
-      <c r="BC8" s="145"/>
-      <c r="BF8" s="40"/>
+      <c r="A8" s="128"/>
+      <c r="B8" s="129"/>
+      <c r="C8" s="125"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="75"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="75"/>
+      <c r="M8" s="56"/>
+      <c r="N8" s="75"/>
+      <c r="O8" s="56"/>
+      <c r="P8" s="75"/>
+      <c r="Q8" s="56"/>
+      <c r="R8" s="120"/>
+      <c r="S8" s="122"/>
+      <c r="T8" s="138"/>
+      <c r="U8" s="139"/>
+      <c r="V8" s="138"/>
+      <c r="W8" s="139"/>
+      <c r="X8" s="138"/>
+      <c r="Y8" s="139"/>
+      <c r="Z8" s="138"/>
+      <c r="AA8" s="139"/>
+      <c r="AB8" s="141"/>
+      <c r="AC8" s="139"/>
+      <c r="AD8" s="138"/>
+      <c r="AE8" s="139"/>
+      <c r="AF8" s="120"/>
+      <c r="AG8" s="56"/>
+      <c r="AH8" s="55"/>
+      <c r="AI8" s="56"/>
+      <c r="AJ8" s="55"/>
+      <c r="AK8" s="56"/>
+      <c r="AL8" s="55"/>
+      <c r="AM8" s="56"/>
+      <c r="AN8" s="55"/>
+      <c r="AO8" s="56"/>
+      <c r="AP8" s="51"/>
+      <c r="AQ8" s="52"/>
+      <c r="AR8" s="51"/>
+      <c r="AS8" s="52"/>
+      <c r="AT8" s="51"/>
+      <c r="AU8" s="52"/>
+      <c r="AV8" s="51"/>
+      <c r="AW8" s="52"/>
+      <c r="AX8" s="51"/>
+      <c r="AY8" s="52"/>
+      <c r="AZ8" s="51"/>
+      <c r="BA8" s="52"/>
+      <c r="BB8" s="54"/>
+      <c r="BC8" s="52"/>
+      <c r="BD8" s="159" t="s">
+        <v>142</v>
+      </c>
+      <c r="BE8" s="159" t="s">
+        <v>143</v>
+      </c>
+      <c r="BF8" s="159" t="s">
+        <v>144</v>
+      </c>
+      <c r="BG8" s="159" t="s">
+        <v>145</v>
+      </c>
+      <c r="BH8" s="160" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="9" spans="1:63" s="10" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
-      <c r="A9" s="68"/>
-      <c r="B9" s="69"/>
+      <c r="A9" s="130"/>
+      <c r="B9" s="131"/>
       <c r="C9" s="20" t="s">
         <v>37</v>
       </c>
@@ -3231,10 +3378,24 @@
       <c r="BC9" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="BF9" s="40"/>
+      <c r="BD9" s="161" t="s">
+        <v>141</v>
+      </c>
+      <c r="BE9" s="161" t="s">
+        <v>141</v>
+      </c>
+      <c r="BF9" s="161" t="s">
+        <v>141</v>
+      </c>
+      <c r="BG9" s="161" t="s">
+        <v>141</v>
+      </c>
+      <c r="BH9" s="161" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="10" spans="1:63" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="116" t="s">
         <v>42</v>
       </c>
       <c r="B10" s="27" t="s">
@@ -3448,14 +3609,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A1)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC10" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A1)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF10" s="40"/>
+      <c r="BC10" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A1)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD10" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A1)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE10" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A1)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF10" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A1)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG10" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A1)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH10" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A1)-1)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:63" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A11" s="70"/>
+      <c r="A11" s="132"/>
       <c r="B11" s="27" t="s">
         <v>45</v>
       </c>
@@ -3667,14 +3847,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A2)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC11" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A2)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF11" s="40"/>
+      <c r="BC11" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A2)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD11" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A2)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE11" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A2)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF11" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A2)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG11" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A2)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH11" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A2)-1)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:63" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A12" s="71"/>
+      <c r="A12" s="133"/>
       <c r="B12" s="27" t="s">
         <v>47</v>
       </c>
@@ -3886,14 +4085,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A3)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC12" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A3)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF12" s="40"/>
+      <c r="BC12" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A3)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD12" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A3)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE12" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A3)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF12" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A3)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG12" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A3)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH12" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A3)-1)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:63" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A13" s="71"/>
+      <c r="A13" s="133"/>
       <c r="B13" s="27" t="s">
         <v>49</v>
       </c>
@@ -4105,14 +4323,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A4)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC13" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A4)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF13" s="40"/>
+      <c r="BC13" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A4)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD13" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A4)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE13" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A4)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF13" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A4)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG13" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A4)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH13" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A4)-1)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:63" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A14" s="71"/>
+      <c r="A14" s="133"/>
       <c r="B14" s="27" t="s">
         <v>51</v>
       </c>
@@ -4324,14 +4561,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A5)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC14" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A5)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF14" s="40"/>
+      <c r="BC14" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A5)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD14" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A5)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE14" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A5)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF14" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A5)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG14" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A5)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH14" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A5)-1)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:63" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A15" s="71"/>
+      <c r="A15" s="133"/>
       <c r="B15" s="27" t="s">
         <v>53</v>
       </c>
@@ -4543,14 +4799,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A6)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC15" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A6)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF15" s="40"/>
+      <c r="BC15" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A6)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD15" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A6)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE15" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A6)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF15" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A6)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG15" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A6)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH15" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A6)-1)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:63" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A16" s="71"/>
+      <c r="A16" s="133"/>
       <c r="B16" s="27" t="s">
         <v>55</v>
       </c>
@@ -4762,14 +5037,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A7)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC16" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A7)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF16" s="40"/>
-    </row>
-    <row r="17" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A17" s="71"/>
+      <c r="BC16" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A7)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD16" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A7)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE16" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A7)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF16" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A7)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG16" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A7)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH16" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A7)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A17" s="133"/>
       <c r="B17" s="27" t="s">
         <v>57</v>
       </c>
@@ -4981,14 +5275,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A8)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC17" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A8)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF17" s="40"/>
-    </row>
-    <row r="18" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A18" s="71"/>
+      <c r="BC17" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A8)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD17" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A8)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE17" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A8)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF17" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A8)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG17" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A8)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH17" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A8)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A18" s="133"/>
       <c r="B18" s="27" t="s">
         <v>59</v>
       </c>
@@ -5200,14 +5513,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A9)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC18" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A9)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF18" s="40"/>
-    </row>
-    <row r="19" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A19" s="72"/>
+      <c r="BC18" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A9)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD18" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A9)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE18" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A9)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF18" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A9)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG18" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A9)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH18" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A9)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A19" s="134"/>
       <c r="B19" s="27" t="s">
         <v>61</v>
       </c>
@@ -5419,14 +5751,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A10)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC19" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A10)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF19" s="40"/>
-    </row>
-    <row r="20" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A20" s="72"/>
+      <c r="BC19" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A10)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD19" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A10)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE19" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A10)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF19" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A10)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG19" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A10)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH19" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A10)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A20" s="134"/>
       <c r="B20" s="27" t="s">
         <v>63</v>
       </c>
@@ -5638,14 +5989,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A11)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC20" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A11)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF20" s="40"/>
-    </row>
-    <row r="21" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A21" s="73"/>
+      <c r="BC20" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A11)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD20" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A11)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE20" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A11)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF20" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A11)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG20" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A11)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH20" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A11)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A21" s="135"/>
       <c r="B21" s="27" t="s">
         <v>65</v>
       </c>
@@ -5857,14 +6227,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A12)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC21" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A12)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF21" s="40"/>
-    </row>
-    <row r="22" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A22" s="57" t="s">
+      <c r="BC21" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A12)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD21" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A12)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE21" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A12)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF21" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A12)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG21" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A12)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH21" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A12)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A22" s="116" t="s">
         <v>42</v>
       </c>
       <c r="B22" s="27" t="s">
@@ -6078,14 +6467,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A13)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC22" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A13)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF22" s="40"/>
-    </row>
-    <row r="23" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A23" s="70"/>
+      <c r="BC22" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A13)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD22" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A13)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE22" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A13)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF22" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A13)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG22" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A13)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH22" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A13)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A23" s="132"/>
       <c r="B23" s="27" t="s">
         <v>69</v>
       </c>
@@ -6297,14 +6705,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A14)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC23" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A14)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF23" s="40"/>
-    </row>
-    <row r="24" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A24" s="71"/>
+      <c r="BC23" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A14)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD23" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A14)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE23" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A14)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF23" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A14)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG23" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A14)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH23" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A14)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A24" s="133"/>
       <c r="B24" s="27" t="s">
         <v>71</v>
       </c>
@@ -6516,14 +6943,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A15)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC24" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A15)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF24" s="40"/>
-    </row>
-    <row r="25" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A25" s="71"/>
+      <c r="BC24" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A15)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD24" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A15)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE24" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A15)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF24" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A15)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG24" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A15)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH24" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A15)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A25" s="133"/>
       <c r="B25" s="27" t="s">
         <v>73</v>
       </c>
@@ -6735,14 +7181,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A16)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC25" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A16)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF25" s="40"/>
-    </row>
-    <row r="26" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A26" s="71"/>
+      <c r="BC25" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A16)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD25" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A16)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE25" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A16)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF25" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A16)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG25" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A16)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH25" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A16)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A26" s="133"/>
       <c r="B26" s="27" t="s">
         <v>75</v>
       </c>
@@ -6954,14 +7419,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A17)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC26" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A17)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF26" s="40"/>
-    </row>
-    <row r="27" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A27" s="71"/>
+      <c r="BC26" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A17)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD26" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A17)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE26" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A17)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF26" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A17)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG26" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A17)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH26" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A17)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A27" s="133"/>
       <c r="B27" s="27" t="s">
         <v>77</v>
       </c>
@@ -7173,14 +7657,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A18)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC27" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A18)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF27" s="40"/>
-    </row>
-    <row r="28" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A28" s="71"/>
+      <c r="BC27" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A18)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD27" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A18)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE27" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A18)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF27" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A18)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG27" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A18)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH27" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A18)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A28" s="133"/>
       <c r="B28" s="27" t="s">
         <v>79</v>
       </c>
@@ -7392,14 +7895,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A19)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC28" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A19)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF28" s="40"/>
-    </row>
-    <row r="29" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A29" s="71"/>
+      <c r="BC28" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A19)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD28" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A19)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE28" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A19)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF28" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A19)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG28" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A19)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH28" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A19)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A29" s="133"/>
       <c r="B29" s="27" t="s">
         <v>81</v>
       </c>
@@ -7611,14 +8133,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A20)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC29" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A20)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF29" s="40"/>
-    </row>
-    <row r="30" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A30" s="71"/>
+      <c r="BC29" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A20)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD29" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A20)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE29" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A20)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF29" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A20)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG29" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A20)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH29" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A20)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A30" s="133"/>
       <c r="B30" s="27" t="s">
         <v>83</v>
       </c>
@@ -7830,14 +8371,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A21)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC30" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A21)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF30" s="40"/>
-    </row>
-    <row r="31" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A31" s="72"/>
+      <c r="BC30" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A21)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD30" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A21)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE30" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A21)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF30" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A21)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG30" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A21)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH30" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A21)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A31" s="134"/>
       <c r="B31" s="27" t="s">
         <v>85</v>
       </c>
@@ -8049,14 +8609,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A22)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC31" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A22)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF31" s="40"/>
-    </row>
-    <row r="32" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A32" s="72"/>
+      <c r="BC31" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A22)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD31" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A22)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE31" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A22)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF31" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A22)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG31" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A22)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH31" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A22)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A32" s="134"/>
       <c r="B32" s="27" t="s">
         <v>87</v>
       </c>
@@ -8268,14 +8847,33 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A23)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC32" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A23)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF32" s="40"/>
-    </row>
-    <row r="33" spans="1:58" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A33" s="73"/>
+      <c r="BC32" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A23)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD32" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A23)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE32" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A23)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF32" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A23)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG32" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A23)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH32" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A23)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:60" s="10" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A33" s="135"/>
       <c r="B33" s="27" t="s">
         <v>89</v>
       </c>
@@ -8487,730 +9085,757 @@
         <f ca="1">OFFSET(Sheet2!$D$57,0,ROW(A24)-1)</f>
         <v>0</v>
       </c>
-      <c r="BC33" s="34">
-        <f ca="1">OFFSET(Sheet2!$D$48,0,ROW(A24)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="BF33" s="40"/>
-    </row>
-    <row r="34" spans="1:58" s="12" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A34" s="88" t="s">
+      <c r="BC33" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$58,0,ROW(A24)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BD33" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$59,0,ROW(A24)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BE33" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$60,0,ROW(A24)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BF33" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$61,0,ROW(A24)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BG33" s="33">
+        <f ca="1">OFFSET(Sheet2!$D$62,0,ROW(A24)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="BH33" s="32">
+        <f ca="1">OFFSET(Sheet2!$D$63,0,ROW(A24)-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:60" s="12" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A34" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="B34" s="88"/>
-      <c r="C34" s="88"/>
-      <c r="D34" s="88"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="88"/>
-      <c r="G34" s="88"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="88"/>
-      <c r="J34" s="88"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="88"/>
-      <c r="M34" s="88"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="88"/>
-      <c r="P34" s="88"/>
-      <c r="Q34" s="89"/>
-      <c r="R34" s="124" t="s">
+      <c r="B34" s="77"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="77"/>
+      <c r="K34" s="77"/>
+      <c r="L34" s="77"/>
+      <c r="M34" s="77"/>
+      <c r="N34" s="77"/>
+      <c r="O34" s="77"/>
+      <c r="P34" s="77"/>
+      <c r="Q34" s="78"/>
+      <c r="R34" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="S34" s="124"/>
-      <c r="T34" s="124"/>
-      <c r="U34" s="124"/>
-      <c r="V34" s="124"/>
-      <c r="W34" s="124"/>
-      <c r="X34" s="124"/>
-      <c r="Y34" s="124"/>
-      <c r="Z34" s="124"/>
-      <c r="AA34" s="124"/>
-      <c r="AB34" s="124"/>
-      <c r="AC34" s="124"/>
-      <c r="AD34" s="124"/>
-      <c r="AE34" s="124"/>
-      <c r="AF34" s="124"/>
-      <c r="AG34" s="124"/>
-      <c r="AH34" s="124"/>
-      <c r="AI34" s="124"/>
-      <c r="AJ34" s="124"/>
-      <c r="AK34" s="124"/>
-      <c r="AL34" s="124"/>
-      <c r="AM34" s="124"/>
-      <c r="AN34" s="124"/>
-      <c r="AO34" s="124"/>
-      <c r="AP34" s="124"/>
-      <c r="AQ34" s="124"/>
-      <c r="AR34" s="124"/>
-      <c r="AS34" s="124"/>
-      <c r="AT34" s="124"/>
-      <c r="AU34" s="125"/>
-      <c r="AV34" s="126" t="s">
+      <c r="S34" s="66"/>
+      <c r="T34" s="66"/>
+      <c r="U34" s="66"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="66"/>
+      <c r="X34" s="66"/>
+      <c r="Y34" s="66"/>
+      <c r="Z34" s="66"/>
+      <c r="AA34" s="66"/>
+      <c r="AB34" s="66"/>
+      <c r="AC34" s="66"/>
+      <c r="AD34" s="66"/>
+      <c r="AE34" s="66"/>
+      <c r="AF34" s="66"/>
+      <c r="AG34" s="66"/>
+      <c r="AH34" s="66"/>
+      <c r="AI34" s="66"/>
+      <c r="AJ34" s="66"/>
+      <c r="AK34" s="66"/>
+      <c r="AL34" s="66"/>
+      <c r="AM34" s="66"/>
+      <c r="AN34" s="66"/>
+      <c r="AO34" s="66"/>
+      <c r="AP34" s="66"/>
+      <c r="AQ34" s="66"/>
+      <c r="AR34" s="66"/>
+      <c r="AS34" s="66"/>
+      <c r="AT34" s="66"/>
+      <c r="AU34" s="67"/>
+      <c r="AV34" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="AW34" s="127"/>
-      <c r="AX34" s="127"/>
-      <c r="AY34" s="127"/>
-      <c r="AZ34" s="127"/>
-      <c r="BA34" s="127"/>
-      <c r="BB34" s="127"/>
-      <c r="BC34" s="128"/>
-      <c r="BF34" s="40"/>
-    </row>
-    <row r="35" spans="1:58" s="10" customFormat="1" ht="30" customHeight="1">
-      <c r="A35" s="57" t="s">
+      <c r="AW34" s="69"/>
+      <c r="AX34" s="69"/>
+      <c r="AY34" s="69"/>
+      <c r="AZ34" s="69"/>
+      <c r="BA34" s="69"/>
+      <c r="BB34" s="69"/>
+      <c r="BC34" s="165"/>
+      <c r="BD34" s="164"/>
+      <c r="BE34" s="164"/>
+      <c r="BF34" s="164"/>
+      <c r="BG34" s="164"/>
+      <c r="BH34" s="164"/>
+    </row>
+    <row r="35" spans="1:60" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A35" s="116" t="s">
         <v>94</v>
       </c>
-      <c r="B35" s="57" t="s">
+      <c r="B35" s="116" t="s">
         <v>95</v>
       </c>
-      <c r="C35" s="90" t="s">
+      <c r="C35" s="92" t="s">
         <v>96</v>
       </c>
-      <c r="D35" s="93"/>
-      <c r="E35" s="93"/>
-      <c r="F35" s="93"/>
-      <c r="G35" s="93"/>
-      <c r="H35" s="93"/>
-      <c r="I35" s="93"/>
-      <c r="J35" s="93"/>
-      <c r="K35" s="93"/>
-      <c r="L35" s="93"/>
-      <c r="M35" s="93"/>
-      <c r="N35" s="93"/>
-      <c r="O35" s="93"/>
-      <c r="P35" s="93"/>
-      <c r="Q35" s="91"/>
-      <c r="R35" s="90" t="s">
+      <c r="D35" s="115"/>
+      <c r="E35" s="115"/>
+      <c r="F35" s="115"/>
+      <c r="G35" s="115"/>
+      <c r="H35" s="115"/>
+      <c r="I35" s="115"/>
+      <c r="J35" s="115"/>
+      <c r="K35" s="115"/>
+      <c r="L35" s="115"/>
+      <c r="M35" s="115"/>
+      <c r="N35" s="115"/>
+      <c r="O35" s="115"/>
+      <c r="P35" s="115"/>
+      <c r="Q35" s="93"/>
+      <c r="R35" s="92" t="s">
         <v>94</v>
       </c>
-      <c r="S35" s="91"/>
-      <c r="T35" s="36"/>
-      <c r="U35" s="36"/>
-      <c r="V35" s="36"/>
-      <c r="W35" s="36"/>
-      <c r="X35" s="36"/>
-      <c r="Y35" s="36"/>
-      <c r="Z35" s="36"/>
-      <c r="AA35" s="36"/>
-      <c r="AB35" s="36"/>
-      <c r="AC35" s="36"/>
-      <c r="AD35" s="36"/>
-      <c r="AE35" s="36"/>
-      <c r="AF35" s="90" t="s">
+      <c r="S35" s="93"/>
+      <c r="T35" s="35"/>
+      <c r="U35" s="35"/>
+      <c r="V35" s="35"/>
+      <c r="W35" s="35"/>
+      <c r="X35" s="35"/>
+      <c r="Y35" s="35"/>
+      <c r="Z35" s="35"/>
+      <c r="AA35" s="35"/>
+      <c r="AB35" s="35"/>
+      <c r="AC35" s="35"/>
+      <c r="AD35" s="35"/>
+      <c r="AE35" s="35"/>
+      <c r="AF35" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="AG35" s="91"/>
-      <c r="AH35" s="90" t="s">
+      <c r="AG35" s="93"/>
+      <c r="AH35" s="92" t="s">
         <v>96</v>
       </c>
-      <c r="AI35" s="93"/>
-      <c r="AJ35" s="93"/>
-      <c r="AK35" s="93"/>
-      <c r="AL35" s="93"/>
-      <c r="AM35" s="93"/>
-      <c r="AN35" s="93"/>
-      <c r="AO35" s="93"/>
-      <c r="AP35" s="93"/>
-      <c r="AQ35" s="93"/>
-      <c r="AR35" s="93"/>
-      <c r="AS35" s="93"/>
-      <c r="AT35" s="93"/>
-      <c r="AU35" s="91"/>
-      <c r="AV35" s="129"/>
-      <c r="AW35" s="129"/>
-      <c r="AX35" s="129"/>
-      <c r="AY35" s="129"/>
-      <c r="AZ35" s="129"/>
-      <c r="BA35" s="129"/>
-      <c r="BB35" s="129"/>
-      <c r="BC35" s="130"/>
-      <c r="BF35" s="40"/>
-    </row>
-    <row r="36" spans="1:58" s="10" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A36" s="58"/>
-      <c r="B36" s="58"/>
-      <c r="C36" s="92"/>
-      <c r="D36" s="86"/>
-      <c r="E36" s="86"/>
-      <c r="F36" s="86"/>
-      <c r="G36" s="86"/>
-      <c r="H36" s="86"/>
-      <c r="I36" s="86"/>
-      <c r="J36" s="86"/>
-      <c r="K36" s="86"/>
-      <c r="L36" s="86"/>
-      <c r="M36" s="86"/>
-      <c r="N36" s="86"/>
-      <c r="O36" s="86"/>
-      <c r="P36" s="86"/>
-      <c r="Q36" s="87"/>
-      <c r="R36" s="92"/>
-      <c r="S36" s="87"/>
-      <c r="T36" s="35"/>
-      <c r="U36" s="35"/>
-      <c r="V36" s="35"/>
-      <c r="W36" s="35"/>
-      <c r="X36" s="35"/>
-      <c r="Y36" s="35"/>
-      <c r="Z36" s="35"/>
-      <c r="AA36" s="35"/>
-      <c r="AB36" s="35"/>
-      <c r="AC36" s="35"/>
-      <c r="AD36" s="35"/>
-      <c r="AE36" s="35"/>
-      <c r="AF36" s="92"/>
-      <c r="AG36" s="87"/>
-      <c r="AH36" s="92"/>
-      <c r="AI36" s="86"/>
-      <c r="AJ36" s="86"/>
-      <c r="AK36" s="86"/>
-      <c r="AL36" s="86"/>
-      <c r="AM36" s="86"/>
-      <c r="AN36" s="86"/>
-      <c r="AO36" s="86"/>
-      <c r="AP36" s="86"/>
-      <c r="AQ36" s="86"/>
-      <c r="AR36" s="86"/>
-      <c r="AS36" s="86"/>
-      <c r="AT36" s="86"/>
-      <c r="AU36" s="87"/>
-      <c r="AV36" s="131"/>
-      <c r="AW36" s="131"/>
-      <c r="AX36" s="131"/>
-      <c r="AY36" s="131"/>
-      <c r="AZ36" s="131"/>
-      <c r="BA36" s="131"/>
-      <c r="BB36" s="131"/>
-      <c r="BC36" s="132"/>
-      <c r="BF36" s="40"/>
-    </row>
-    <row r="37" spans="1:58" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="AI35" s="115"/>
+      <c r="AJ35" s="115"/>
+      <c r="AK35" s="115"/>
+      <c r="AL35" s="115"/>
+      <c r="AM35" s="115"/>
+      <c r="AN35" s="115"/>
+      <c r="AO35" s="115"/>
+      <c r="AP35" s="115"/>
+      <c r="AQ35" s="115"/>
+      <c r="AR35" s="115"/>
+      <c r="AS35" s="115"/>
+      <c r="AT35" s="115"/>
+      <c r="AU35" s="93"/>
+      <c r="AV35" s="166"/>
+      <c r="AW35" s="163"/>
+      <c r="AX35" s="163"/>
+      <c r="AY35" s="163"/>
+      <c r="AZ35" s="163"/>
+      <c r="BA35" s="163"/>
+      <c r="BB35" s="163"/>
+      <c r="BC35" s="167"/>
+      <c r="BD35" s="164"/>
+      <c r="BE35" s="164"/>
+      <c r="BF35" s="164"/>
+      <c r="BG35" s="164"/>
+      <c r="BH35" s="164"/>
+    </row>
+    <row r="36" spans="1:60" s="10" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A36" s="117"/>
+      <c r="B36" s="117"/>
+      <c r="C36" s="94"/>
+      <c r="D36" s="114"/>
+      <c r="E36" s="114"/>
+      <c r="F36" s="114"/>
+      <c r="G36" s="114"/>
+      <c r="H36" s="114"/>
+      <c r="I36" s="114"/>
+      <c r="J36" s="114"/>
+      <c r="K36" s="114"/>
+      <c r="L36" s="114"/>
+      <c r="M36" s="114"/>
+      <c r="N36" s="114"/>
+      <c r="O36" s="114"/>
+      <c r="P36" s="114"/>
+      <c r="Q36" s="95"/>
+      <c r="R36" s="94"/>
+      <c r="S36" s="95"/>
+      <c r="T36" s="34"/>
+      <c r="U36" s="34"/>
+      <c r="V36" s="34"/>
+      <c r="W36" s="34"/>
+      <c r="X36" s="34"/>
+      <c r="Y36" s="34"/>
+      <c r="Z36" s="34"/>
+      <c r="AA36" s="34"/>
+      <c r="AB36" s="34"/>
+      <c r="AC36" s="34"/>
+      <c r="AD36" s="34"/>
+      <c r="AE36" s="34"/>
+      <c r="AF36" s="94"/>
+      <c r="AG36" s="95"/>
+      <c r="AH36" s="94"/>
+      <c r="AI36" s="114"/>
+      <c r="AJ36" s="114"/>
+      <c r="AK36" s="114"/>
+      <c r="AL36" s="114"/>
+      <c r="AM36" s="114"/>
+      <c r="AN36" s="114"/>
+      <c r="AO36" s="114"/>
+      <c r="AP36" s="114"/>
+      <c r="AQ36" s="114"/>
+      <c r="AR36" s="114"/>
+      <c r="AS36" s="114"/>
+      <c r="AT36" s="114"/>
+      <c r="AU36" s="95"/>
+      <c r="AV36" s="168"/>
+      <c r="AW36" s="70"/>
+      <c r="AX36" s="70"/>
+      <c r="AY36" s="70"/>
+      <c r="AZ36" s="70"/>
+      <c r="BA36" s="70"/>
+      <c r="BB36" s="70"/>
+      <c r="BC36" s="169"/>
+      <c r="BF36" s="39"/>
+    </row>
+    <row r="37" spans="1:60" s="10" customFormat="1" ht="30" customHeight="1">
       <c r="A37" s="29"/>
       <c r="B37" s="29"/>
-      <c r="C37" s="133"/>
-      <c r="D37" s="133"/>
-      <c r="E37" s="133"/>
-      <c r="F37" s="133"/>
-      <c r="G37" s="133"/>
-      <c r="H37" s="133"/>
-      <c r="I37" s="133"/>
-      <c r="J37" s="133"/>
-      <c r="K37" s="133"/>
-      <c r="L37" s="133"/>
-      <c r="M37" s="133"/>
-      <c r="N37" s="133"/>
-      <c r="O37" s="133"/>
-      <c r="P37" s="133"/>
-      <c r="Q37" s="133"/>
-      <c r="R37" s="94"/>
-      <c r="S37" s="95"/>
-      <c r="T37" s="37"/>
-      <c r="U37" s="37"/>
-      <c r="V37" s="37"/>
-      <c r="W37" s="37"/>
-      <c r="X37" s="37"/>
-      <c r="Y37" s="37"/>
-      <c r="Z37" s="37"/>
-      <c r="AA37" s="37"/>
-      <c r="AB37" s="37"/>
-      <c r="AC37" s="37"/>
-      <c r="AD37" s="37"/>
-      <c r="AE37" s="37"/>
-      <c r="AF37" s="94"/>
-      <c r="AG37" s="95"/>
-      <c r="AH37" s="82"/>
-      <c r="AI37" s="83"/>
-      <c r="AJ37" s="83"/>
-      <c r="AK37" s="83"/>
-      <c r="AL37" s="83"/>
-      <c r="AM37" s="83"/>
-      <c r="AN37" s="83"/>
-      <c r="AO37" s="83"/>
-      <c r="AP37" s="83"/>
-      <c r="AQ37" s="83"/>
-      <c r="AR37" s="83"/>
-      <c r="AS37" s="83"/>
-      <c r="AT37" s="83"/>
-      <c r="AU37" s="84"/>
-      <c r="AV37" s="115"/>
-      <c r="AW37" s="116"/>
-      <c r="AX37" s="116"/>
-      <c r="AY37" s="116"/>
-      <c r="AZ37" s="116"/>
-      <c r="BA37" s="116"/>
-      <c r="BB37" s="116"/>
-      <c r="BC37" s="117"/>
-      <c r="BF37" s="40"/>
-    </row>
-    <row r="38" spans="1:58" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="C37" s="71"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="71"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="71"/>
+      <c r="K37" s="71"/>
+      <c r="L37" s="71"/>
+      <c r="M37" s="71"/>
+      <c r="N37" s="71"/>
+      <c r="O37" s="71"/>
+      <c r="P37" s="71"/>
+      <c r="Q37" s="71"/>
+      <c r="R37" s="96"/>
+      <c r="S37" s="97"/>
+      <c r="T37" s="36"/>
+      <c r="U37" s="36"/>
+      <c r="V37" s="36"/>
+      <c r="W37" s="36"/>
+      <c r="X37" s="36"/>
+      <c r="Y37" s="36"/>
+      <c r="Z37" s="36"/>
+      <c r="AA37" s="36"/>
+      <c r="AB37" s="36"/>
+      <c r="AC37" s="36"/>
+      <c r="AD37" s="36"/>
+      <c r="AE37" s="36"/>
+      <c r="AF37" s="96"/>
+      <c r="AG37" s="97"/>
+      <c r="AH37" s="110"/>
+      <c r="AI37" s="111"/>
+      <c r="AJ37" s="111"/>
+      <c r="AK37" s="111"/>
+      <c r="AL37" s="111"/>
+      <c r="AM37" s="111"/>
+      <c r="AN37" s="111"/>
+      <c r="AO37" s="111"/>
+      <c r="AP37" s="111"/>
+      <c r="AQ37" s="111"/>
+      <c r="AR37" s="111"/>
+      <c r="AS37" s="111"/>
+      <c r="AT37" s="111"/>
+      <c r="AU37" s="112"/>
+      <c r="AV37" s="57"/>
+      <c r="AW37" s="58"/>
+      <c r="AX37" s="58"/>
+      <c r="AY37" s="58"/>
+      <c r="AZ37" s="58"/>
+      <c r="BA37" s="58"/>
+      <c r="BB37" s="58"/>
+      <c r="BC37" s="59"/>
+      <c r="BF37" s="39"/>
+    </row>
+    <row r="38" spans="1:60" s="10" customFormat="1" ht="30" customHeight="1">
       <c r="A38" s="11"/>
       <c r="B38" s="11"/>
-      <c r="C38" s="107"/>
-      <c r="D38" s="107"/>
-      <c r="E38" s="107"/>
-      <c r="F38" s="107"/>
-      <c r="G38" s="107"/>
-      <c r="H38" s="107"/>
-      <c r="I38" s="107"/>
-      <c r="J38" s="107"/>
-      <c r="K38" s="107"/>
-      <c r="L38" s="107"/>
-      <c r="M38" s="107"/>
-      <c r="N38" s="107"/>
-      <c r="O38" s="107"/>
-      <c r="P38" s="107"/>
-      <c r="Q38" s="107"/>
-      <c r="R38" s="96"/>
-      <c r="S38" s="97"/>
-      <c r="T38" s="38"/>
-      <c r="U38" s="38"/>
-      <c r="V38" s="38"/>
-      <c r="W38" s="38"/>
-      <c r="X38" s="38"/>
-      <c r="Y38" s="38"/>
-      <c r="Z38" s="38"/>
-      <c r="AA38" s="38"/>
-      <c r="AB38" s="38"/>
-      <c r="AC38" s="38"/>
-      <c r="AD38" s="38"/>
-      <c r="AE38" s="38"/>
-      <c r="AF38" s="96"/>
-      <c r="AG38" s="97"/>
-      <c r="AH38" s="82"/>
-      <c r="AI38" s="83"/>
-      <c r="AJ38" s="83"/>
-      <c r="AK38" s="83"/>
-      <c r="AL38" s="83"/>
-      <c r="AM38" s="83"/>
-      <c r="AN38" s="83"/>
-      <c r="AO38" s="83"/>
-      <c r="AP38" s="83"/>
-      <c r="AQ38" s="83"/>
-      <c r="AR38" s="83"/>
-      <c r="AS38" s="83"/>
-      <c r="AT38" s="83"/>
-      <c r="AU38" s="84"/>
-      <c r="AV38" s="118"/>
-      <c r="AW38" s="119"/>
-      <c r="AX38" s="119"/>
-      <c r="AY38" s="119"/>
-      <c r="AZ38" s="119"/>
-      <c r="BA38" s="119"/>
-      <c r="BB38" s="119"/>
-      <c r="BC38" s="120"/>
-      <c r="BF38" s="40"/>
-    </row>
-    <row r="39" spans="1:58" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="C38" s="102"/>
+      <c r="D38" s="102"/>
+      <c r="E38" s="102"/>
+      <c r="F38" s="102"/>
+      <c r="G38" s="102"/>
+      <c r="H38" s="102"/>
+      <c r="I38" s="102"/>
+      <c r="J38" s="102"/>
+      <c r="K38" s="102"/>
+      <c r="L38" s="102"/>
+      <c r="M38" s="102"/>
+      <c r="N38" s="102"/>
+      <c r="O38" s="102"/>
+      <c r="P38" s="102"/>
+      <c r="Q38" s="102"/>
+      <c r="R38" s="98"/>
+      <c r="S38" s="99"/>
+      <c r="T38" s="37"/>
+      <c r="U38" s="37"/>
+      <c r="V38" s="37"/>
+      <c r="W38" s="37"/>
+      <c r="X38" s="37"/>
+      <c r="Y38" s="37"/>
+      <c r="Z38" s="37"/>
+      <c r="AA38" s="37"/>
+      <c r="AB38" s="37"/>
+      <c r="AC38" s="37"/>
+      <c r="AD38" s="37"/>
+      <c r="AE38" s="37"/>
+      <c r="AF38" s="98"/>
+      <c r="AG38" s="99"/>
+      <c r="AH38" s="110"/>
+      <c r="AI38" s="111"/>
+      <c r="AJ38" s="111"/>
+      <c r="AK38" s="111"/>
+      <c r="AL38" s="111"/>
+      <c r="AM38" s="111"/>
+      <c r="AN38" s="111"/>
+      <c r="AO38" s="111"/>
+      <c r="AP38" s="111"/>
+      <c r="AQ38" s="111"/>
+      <c r="AR38" s="111"/>
+      <c r="AS38" s="111"/>
+      <c r="AT38" s="111"/>
+      <c r="AU38" s="112"/>
+      <c r="AV38" s="60"/>
+      <c r="AW38" s="61"/>
+      <c r="AX38" s="61"/>
+      <c r="AY38" s="61"/>
+      <c r="AZ38" s="61"/>
+      <c r="BA38" s="61"/>
+      <c r="BB38" s="61"/>
+      <c r="BC38" s="62"/>
+      <c r="BF38" s="39"/>
+    </row>
+    <row r="39" spans="1:60" s="10" customFormat="1" ht="30" customHeight="1">
       <c r="A39" s="11"/>
       <c r="B39" s="11"/>
-      <c r="C39" s="107"/>
-      <c r="D39" s="107"/>
-      <c r="E39" s="107"/>
-      <c r="F39" s="107"/>
-      <c r="G39" s="107"/>
-      <c r="H39" s="107"/>
-      <c r="I39" s="107"/>
-      <c r="J39" s="107"/>
-      <c r="K39" s="107"/>
-      <c r="L39" s="107"/>
-      <c r="M39" s="107"/>
-      <c r="N39" s="107"/>
-      <c r="O39" s="107"/>
-      <c r="P39" s="107"/>
-      <c r="Q39" s="107"/>
-      <c r="R39" s="96"/>
-      <c r="S39" s="97"/>
-      <c r="T39" s="38"/>
-      <c r="U39" s="38"/>
-      <c r="V39" s="38"/>
-      <c r="W39" s="38"/>
-      <c r="X39" s="38"/>
-      <c r="Y39" s="38"/>
-      <c r="Z39" s="38"/>
-      <c r="AA39" s="38"/>
-      <c r="AB39" s="38"/>
-      <c r="AC39" s="38"/>
-      <c r="AD39" s="38"/>
-      <c r="AE39" s="38"/>
-      <c r="AF39" s="96"/>
-      <c r="AG39" s="97"/>
-      <c r="AH39" s="82"/>
-      <c r="AI39" s="83"/>
-      <c r="AJ39" s="83"/>
-      <c r="AK39" s="83"/>
-      <c r="AL39" s="83"/>
-      <c r="AM39" s="83"/>
-      <c r="AN39" s="83"/>
-      <c r="AO39" s="83"/>
-      <c r="AP39" s="83"/>
-      <c r="AQ39" s="83"/>
-      <c r="AR39" s="83"/>
-      <c r="AS39" s="83"/>
-      <c r="AT39" s="83"/>
-      <c r="AU39" s="84"/>
-      <c r="AV39" s="118"/>
-      <c r="AW39" s="119"/>
-      <c r="AX39" s="119"/>
-      <c r="AY39" s="119"/>
-      <c r="AZ39" s="119"/>
-      <c r="BA39" s="119"/>
-      <c r="BB39" s="119"/>
-      <c r="BC39" s="120"/>
-      <c r="BF39" s="40"/>
-    </row>
-    <row r="40" spans="1:58" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="C39" s="102"/>
+      <c r="D39" s="102"/>
+      <c r="E39" s="102"/>
+      <c r="F39" s="102"/>
+      <c r="G39" s="102"/>
+      <c r="H39" s="102"/>
+      <c r="I39" s="102"/>
+      <c r="J39" s="102"/>
+      <c r="K39" s="102"/>
+      <c r="L39" s="102"/>
+      <c r="M39" s="102"/>
+      <c r="N39" s="102"/>
+      <c r="O39" s="102"/>
+      <c r="P39" s="102"/>
+      <c r="Q39" s="102"/>
+      <c r="R39" s="98"/>
+      <c r="S39" s="99"/>
+      <c r="T39" s="37"/>
+      <c r="U39" s="37"/>
+      <c r="V39" s="37"/>
+      <c r="W39" s="37"/>
+      <c r="X39" s="37"/>
+      <c r="Y39" s="37"/>
+      <c r="Z39" s="37"/>
+      <c r="AA39" s="37"/>
+      <c r="AB39" s="37"/>
+      <c r="AC39" s="37"/>
+      <c r="AD39" s="37"/>
+      <c r="AE39" s="37"/>
+      <c r="AF39" s="98"/>
+      <c r="AG39" s="99"/>
+      <c r="AH39" s="110"/>
+      <c r="AI39" s="111"/>
+      <c r="AJ39" s="111"/>
+      <c r="AK39" s="111"/>
+      <c r="AL39" s="111"/>
+      <c r="AM39" s="111"/>
+      <c r="AN39" s="111"/>
+      <c r="AO39" s="111"/>
+      <c r="AP39" s="111"/>
+      <c r="AQ39" s="111"/>
+      <c r="AR39" s="111"/>
+      <c r="AS39" s="111"/>
+      <c r="AT39" s="111"/>
+      <c r="AU39" s="112"/>
+      <c r="AV39" s="60"/>
+      <c r="AW39" s="61"/>
+      <c r="AX39" s="61"/>
+      <c r="AY39" s="61"/>
+      <c r="AZ39" s="61"/>
+      <c r="BA39" s="61"/>
+      <c r="BB39" s="61"/>
+      <c r="BC39" s="62"/>
+      <c r="BF39" s="39"/>
+    </row>
+    <row r="40" spans="1:60" s="10" customFormat="1" ht="30" customHeight="1">
       <c r="A40" s="11"/>
       <c r="B40" s="11"/>
-      <c r="C40" s="107"/>
-      <c r="D40" s="107"/>
-      <c r="E40" s="107"/>
-      <c r="F40" s="107"/>
-      <c r="G40" s="107"/>
-      <c r="H40" s="107"/>
-      <c r="I40" s="107"/>
-      <c r="J40" s="107"/>
-      <c r="K40" s="107"/>
-      <c r="L40" s="107"/>
-      <c r="M40" s="107"/>
-      <c r="N40" s="107"/>
-      <c r="O40" s="107"/>
-      <c r="P40" s="107"/>
-      <c r="Q40" s="107"/>
-      <c r="R40" s="96"/>
-      <c r="S40" s="97"/>
-      <c r="T40" s="38"/>
-      <c r="U40" s="38"/>
-      <c r="V40" s="38"/>
-      <c r="W40" s="38"/>
-      <c r="X40" s="38"/>
-      <c r="Y40" s="38"/>
-      <c r="Z40" s="38"/>
-      <c r="AA40" s="38"/>
-      <c r="AB40" s="38"/>
-      <c r="AC40" s="38"/>
-      <c r="AD40" s="38"/>
-      <c r="AE40" s="38"/>
-      <c r="AF40" s="96"/>
-      <c r="AG40" s="97"/>
-      <c r="AH40" s="82"/>
-      <c r="AI40" s="83"/>
-      <c r="AJ40" s="83"/>
-      <c r="AK40" s="83"/>
-      <c r="AL40" s="83"/>
-      <c r="AM40" s="83"/>
-      <c r="AN40" s="83"/>
-      <c r="AO40" s="83"/>
-      <c r="AP40" s="83"/>
-      <c r="AQ40" s="83"/>
-      <c r="AR40" s="83"/>
-      <c r="AS40" s="83"/>
-      <c r="AT40" s="83"/>
-      <c r="AU40" s="84"/>
-      <c r="AV40" s="118"/>
-      <c r="AW40" s="119"/>
-      <c r="AX40" s="119"/>
-      <c r="AY40" s="119"/>
-      <c r="AZ40" s="119"/>
-      <c r="BA40" s="119"/>
-      <c r="BB40" s="119"/>
-      <c r="BC40" s="120"/>
-      <c r="BF40" s="40"/>
-    </row>
-    <row r="41" spans="1:58" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="C40" s="102"/>
+      <c r="D40" s="102"/>
+      <c r="E40" s="102"/>
+      <c r="F40" s="102"/>
+      <c r="G40" s="102"/>
+      <c r="H40" s="102"/>
+      <c r="I40" s="102"/>
+      <c r="J40" s="102"/>
+      <c r="K40" s="102"/>
+      <c r="L40" s="102"/>
+      <c r="M40" s="102"/>
+      <c r="N40" s="102"/>
+      <c r="O40" s="102"/>
+      <c r="P40" s="102"/>
+      <c r="Q40" s="102"/>
+      <c r="R40" s="98"/>
+      <c r="S40" s="99"/>
+      <c r="T40" s="37"/>
+      <c r="U40" s="37"/>
+      <c r="V40" s="37"/>
+      <c r="W40" s="37"/>
+      <c r="X40" s="37"/>
+      <c r="Y40" s="37"/>
+      <c r="Z40" s="37"/>
+      <c r="AA40" s="37"/>
+      <c r="AB40" s="37"/>
+      <c r="AC40" s="37"/>
+      <c r="AD40" s="37"/>
+      <c r="AE40" s="37"/>
+      <c r="AF40" s="98"/>
+      <c r="AG40" s="99"/>
+      <c r="AH40" s="110"/>
+      <c r="AI40" s="111"/>
+      <c r="AJ40" s="111"/>
+      <c r="AK40" s="111"/>
+      <c r="AL40" s="111"/>
+      <c r="AM40" s="111"/>
+      <c r="AN40" s="111"/>
+      <c r="AO40" s="111"/>
+      <c r="AP40" s="111"/>
+      <c r="AQ40" s="111"/>
+      <c r="AR40" s="111"/>
+      <c r="AS40" s="111"/>
+      <c r="AT40" s="111"/>
+      <c r="AU40" s="112"/>
+      <c r="AV40" s="60"/>
+      <c r="AW40" s="61"/>
+      <c r="AX40" s="61"/>
+      <c r="AY40" s="61"/>
+      <c r="AZ40" s="61"/>
+      <c r="BA40" s="61"/>
+      <c r="BB40" s="61"/>
+      <c r="BC40" s="62"/>
+      <c r="BF40" s="39"/>
+    </row>
+    <row r="41" spans="1:60" s="10" customFormat="1" ht="30" customHeight="1">
       <c r="A41" s="11"/>
       <c r="B41" s="11"/>
-      <c r="C41" s="107"/>
-      <c r="D41" s="107"/>
-      <c r="E41" s="107"/>
-      <c r="F41" s="107"/>
-      <c r="G41" s="107"/>
-      <c r="H41" s="107"/>
-      <c r="I41" s="107"/>
-      <c r="J41" s="107"/>
-      <c r="K41" s="107"/>
-      <c r="L41" s="107"/>
-      <c r="M41" s="107"/>
-      <c r="N41" s="107"/>
-      <c r="O41" s="107"/>
-      <c r="P41" s="107"/>
-      <c r="Q41" s="107"/>
-      <c r="R41" s="96"/>
-      <c r="S41" s="97"/>
-      <c r="T41" s="38"/>
-      <c r="U41" s="38"/>
-      <c r="V41" s="38"/>
-      <c r="W41" s="38"/>
-      <c r="X41" s="38"/>
-      <c r="Y41" s="38"/>
-      <c r="Z41" s="38"/>
-      <c r="AA41" s="38"/>
-      <c r="AB41" s="38"/>
-      <c r="AC41" s="38"/>
-      <c r="AD41" s="38"/>
-      <c r="AE41" s="38"/>
-      <c r="AF41" s="96"/>
-      <c r="AG41" s="97"/>
-      <c r="AH41" s="82"/>
-      <c r="AI41" s="83"/>
-      <c r="AJ41" s="83"/>
-      <c r="AK41" s="83"/>
-      <c r="AL41" s="83"/>
-      <c r="AM41" s="83"/>
-      <c r="AN41" s="83"/>
-      <c r="AO41" s="83"/>
-      <c r="AP41" s="83"/>
-      <c r="AQ41" s="83"/>
-      <c r="AR41" s="83"/>
-      <c r="AS41" s="83"/>
-      <c r="AT41" s="83"/>
-      <c r="AU41" s="84"/>
-      <c r="AV41" s="118"/>
-      <c r="AW41" s="119"/>
-      <c r="AX41" s="119"/>
-      <c r="AY41" s="119"/>
-      <c r="AZ41" s="119"/>
-      <c r="BA41" s="119"/>
-      <c r="BB41" s="119"/>
-      <c r="BC41" s="120"/>
-      <c r="BF41" s="40"/>
-    </row>
-    <row r="42" spans="1:58" s="10" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="C41" s="102"/>
+      <c r="D41" s="102"/>
+      <c r="E41" s="102"/>
+      <c r="F41" s="102"/>
+      <c r="G41" s="102"/>
+      <c r="H41" s="102"/>
+      <c r="I41" s="102"/>
+      <c r="J41" s="102"/>
+      <c r="K41" s="102"/>
+      <c r="L41" s="102"/>
+      <c r="M41" s="102"/>
+      <c r="N41" s="102"/>
+      <c r="O41" s="102"/>
+      <c r="P41" s="102"/>
+      <c r="Q41" s="102"/>
+      <c r="R41" s="98"/>
+      <c r="S41" s="99"/>
+      <c r="T41" s="37"/>
+      <c r="U41" s="37"/>
+      <c r="V41" s="37"/>
+      <c r="W41" s="37"/>
+      <c r="X41" s="37"/>
+      <c r="Y41" s="37"/>
+      <c r="Z41" s="37"/>
+      <c r="AA41" s="37"/>
+      <c r="AB41" s="37"/>
+      <c r="AC41" s="37"/>
+      <c r="AD41" s="37"/>
+      <c r="AE41" s="37"/>
+      <c r="AF41" s="98"/>
+      <c r="AG41" s="99"/>
+      <c r="AH41" s="110"/>
+      <c r="AI41" s="111"/>
+      <c r="AJ41" s="111"/>
+      <c r="AK41" s="111"/>
+      <c r="AL41" s="111"/>
+      <c r="AM41" s="111"/>
+      <c r="AN41" s="111"/>
+      <c r="AO41" s="111"/>
+      <c r="AP41" s="111"/>
+      <c r="AQ41" s="111"/>
+      <c r="AR41" s="111"/>
+      <c r="AS41" s="111"/>
+      <c r="AT41" s="111"/>
+      <c r="AU41" s="112"/>
+      <c r="AV41" s="60"/>
+      <c r="AW41" s="61"/>
+      <c r="AX41" s="61"/>
+      <c r="AY41" s="61"/>
+      <c r="AZ41" s="61"/>
+      <c r="BA41" s="61"/>
+      <c r="BB41" s="61"/>
+      <c r="BC41" s="62"/>
+      <c r="BF41" s="39"/>
+    </row>
+    <row r="42" spans="1:60" s="10" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A42" s="28"/>
       <c r="B42" s="28"/>
-      <c r="C42" s="108"/>
-      <c r="D42" s="108"/>
-      <c r="E42" s="108"/>
-      <c r="F42" s="108"/>
-      <c r="G42" s="108"/>
-      <c r="H42" s="108"/>
-      <c r="I42" s="108"/>
-      <c r="J42" s="108"/>
-      <c r="K42" s="108"/>
-      <c r="L42" s="108"/>
-      <c r="M42" s="108"/>
-      <c r="N42" s="108"/>
-      <c r="O42" s="108"/>
-      <c r="P42" s="108"/>
-      <c r="Q42" s="108"/>
-      <c r="R42" s="80"/>
-      <c r="S42" s="81"/>
-      <c r="T42" s="39"/>
-      <c r="U42" s="39"/>
-      <c r="V42" s="39"/>
-      <c r="W42" s="39"/>
-      <c r="X42" s="39"/>
-      <c r="Y42" s="39"/>
-      <c r="Z42" s="39"/>
-      <c r="AA42" s="39"/>
-      <c r="AB42" s="39"/>
-      <c r="AC42" s="39"/>
-      <c r="AD42" s="39"/>
-      <c r="AE42" s="39"/>
-      <c r="AF42" s="80"/>
-      <c r="AG42" s="81"/>
-      <c r="AH42" s="85"/>
-      <c r="AI42" s="86"/>
-      <c r="AJ42" s="86"/>
-      <c r="AK42" s="86"/>
-      <c r="AL42" s="86"/>
-      <c r="AM42" s="86"/>
-      <c r="AN42" s="86"/>
-      <c r="AO42" s="86"/>
-      <c r="AP42" s="86"/>
-      <c r="AQ42" s="86"/>
-      <c r="AR42" s="86"/>
-      <c r="AS42" s="86"/>
-      <c r="AT42" s="86"/>
-      <c r="AU42" s="87"/>
-      <c r="AV42" s="118"/>
-      <c r="AW42" s="119"/>
-      <c r="AX42" s="119"/>
-      <c r="AY42" s="119"/>
-      <c r="AZ42" s="119"/>
-      <c r="BA42" s="119"/>
-      <c r="BB42" s="119"/>
-      <c r="BC42" s="120"/>
-      <c r="BF42" s="40"/>
-    </row>
-    <row r="43" spans="1:58" s="10" customFormat="1" ht="30" customHeight="1">
-      <c r="A43" s="98" t="s">
+      <c r="C42" s="103"/>
+      <c r="D42" s="103"/>
+      <c r="E42" s="103"/>
+      <c r="F42" s="103"/>
+      <c r="G42" s="103"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="103"/>
+      <c r="J42" s="103"/>
+      <c r="K42" s="103"/>
+      <c r="L42" s="103"/>
+      <c r="M42" s="103"/>
+      <c r="N42" s="103"/>
+      <c r="O42" s="103"/>
+      <c r="P42" s="103"/>
+      <c r="Q42" s="103"/>
+      <c r="R42" s="100"/>
+      <c r="S42" s="101"/>
+      <c r="T42" s="38"/>
+      <c r="U42" s="38"/>
+      <c r="V42" s="38"/>
+      <c r="W42" s="38"/>
+      <c r="X42" s="38"/>
+      <c r="Y42" s="38"/>
+      <c r="Z42" s="38"/>
+      <c r="AA42" s="38"/>
+      <c r="AB42" s="38"/>
+      <c r="AC42" s="38"/>
+      <c r="AD42" s="38"/>
+      <c r="AE42" s="38"/>
+      <c r="AF42" s="100"/>
+      <c r="AG42" s="101"/>
+      <c r="AH42" s="113"/>
+      <c r="AI42" s="114"/>
+      <c r="AJ42" s="114"/>
+      <c r="AK42" s="114"/>
+      <c r="AL42" s="114"/>
+      <c r="AM42" s="114"/>
+      <c r="AN42" s="114"/>
+      <c r="AO42" s="114"/>
+      <c r="AP42" s="114"/>
+      <c r="AQ42" s="114"/>
+      <c r="AR42" s="114"/>
+      <c r="AS42" s="114"/>
+      <c r="AT42" s="114"/>
+      <c r="AU42" s="95"/>
+      <c r="AV42" s="60"/>
+      <c r="AW42" s="61"/>
+      <c r="AX42" s="61"/>
+      <c r="AY42" s="61"/>
+      <c r="AZ42" s="61"/>
+      <c r="BA42" s="61"/>
+      <c r="BB42" s="61"/>
+      <c r="BC42" s="62"/>
+      <c r="BF42" s="39"/>
+    </row>
+    <row r="43" spans="1:60" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A43" s="83" t="s">
         <v>105</v>
       </c>
-      <c r="B43" s="99"/>
-      <c r="C43" s="99"/>
-      <c r="D43" s="99"/>
-      <c r="E43" s="99"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="99"/>
-      <c r="J43" s="99"/>
-      <c r="K43" s="99"/>
-      <c r="L43" s="99"/>
-      <c r="M43" s="99"/>
-      <c r="N43" s="99"/>
-      <c r="O43" s="99"/>
-      <c r="P43" s="99"/>
-      <c r="Q43" s="100"/>
-      <c r="R43" s="109" t="s">
+      <c r="B43" s="84"/>
+      <c r="C43" s="84"/>
+      <c r="D43" s="84"/>
+      <c r="E43" s="84"/>
+      <c r="F43" s="84"/>
+      <c r="G43" s="84"/>
+      <c r="H43" s="84"/>
+      <c r="I43" s="84"/>
+      <c r="J43" s="84"/>
+      <c r="K43" s="84"/>
+      <c r="L43" s="84"/>
+      <c r="M43" s="84"/>
+      <c r="N43" s="84"/>
+      <c r="O43" s="84"/>
+      <c r="P43" s="84"/>
+      <c r="Q43" s="85"/>
+      <c r="R43" s="104" t="s">
         <v>105</v>
       </c>
-      <c r="S43" s="109"/>
-      <c r="T43" s="109"/>
-      <c r="U43" s="109"/>
-      <c r="V43" s="109"/>
-      <c r="W43" s="109"/>
-      <c r="X43" s="109"/>
-      <c r="Y43" s="109"/>
-      <c r="Z43" s="109"/>
-      <c r="AA43" s="109"/>
-      <c r="AB43" s="109"/>
-      <c r="AC43" s="109"/>
-      <c r="AD43" s="109"/>
-      <c r="AE43" s="109"/>
-      <c r="AF43" s="109"/>
-      <c r="AG43" s="109"/>
-      <c r="AH43" s="109"/>
-      <c r="AI43" s="109"/>
-      <c r="AJ43" s="109"/>
-      <c r="AK43" s="109"/>
-      <c r="AL43" s="109"/>
-      <c r="AM43" s="109"/>
-      <c r="AN43" s="109"/>
-      <c r="AO43" s="109"/>
-      <c r="AP43" s="109"/>
-      <c r="AQ43" s="109"/>
-      <c r="AR43" s="109"/>
-      <c r="AS43" s="109"/>
-      <c r="AT43" s="109"/>
-      <c r="AU43" s="110"/>
-      <c r="AV43" s="118"/>
-      <c r="AW43" s="119"/>
-      <c r="AX43" s="119"/>
-      <c r="AY43" s="119"/>
-      <c r="AZ43" s="119"/>
-      <c r="BA43" s="119"/>
-      <c r="BB43" s="119"/>
-      <c r="BC43" s="120"/>
-      <c r="BF43" s="40"/>
-    </row>
-    <row r="44" spans="1:58" s="10" customFormat="1" ht="30" customHeight="1">
-      <c r="A44" s="101"/>
-      <c r="B44" s="102"/>
-      <c r="C44" s="102"/>
-      <c r="D44" s="102"/>
-      <c r="E44" s="102"/>
-      <c r="F44" s="102"/>
-      <c r="G44" s="102"/>
-      <c r="H44" s="102"/>
-      <c r="I44" s="102"/>
-      <c r="J44" s="102"/>
-      <c r="K44" s="102"/>
-      <c r="L44" s="102"/>
-      <c r="M44" s="102"/>
-      <c r="N44" s="102"/>
-      <c r="O44" s="102"/>
-      <c r="P44" s="102"/>
-      <c r="Q44" s="103"/>
-      <c r="R44" s="111"/>
-      <c r="S44" s="111"/>
-      <c r="T44" s="111"/>
-      <c r="U44" s="111"/>
-      <c r="V44" s="111"/>
-      <c r="W44" s="111"/>
-      <c r="X44" s="111"/>
-      <c r="Y44" s="111"/>
-      <c r="Z44" s="111"/>
-      <c r="AA44" s="111"/>
-      <c r="AB44" s="111"/>
-      <c r="AC44" s="111"/>
-      <c r="AD44" s="111"/>
-      <c r="AE44" s="111"/>
-      <c r="AF44" s="111"/>
-      <c r="AG44" s="111"/>
-      <c r="AH44" s="111"/>
-      <c r="AI44" s="111"/>
-      <c r="AJ44" s="111"/>
-      <c r="AK44" s="111"/>
-      <c r="AL44" s="111"/>
-      <c r="AM44" s="111"/>
-      <c r="AN44" s="111"/>
-      <c r="AO44" s="111"/>
-      <c r="AP44" s="111"/>
-      <c r="AQ44" s="111"/>
-      <c r="AR44" s="111"/>
-      <c r="AS44" s="111"/>
-      <c r="AT44" s="111"/>
-      <c r="AU44" s="112"/>
-      <c r="AV44" s="118"/>
-      <c r="AW44" s="119"/>
-      <c r="AX44" s="119"/>
-      <c r="AY44" s="119"/>
-      <c r="AZ44" s="119"/>
-      <c r="BA44" s="119"/>
-      <c r="BB44" s="119"/>
-      <c r="BC44" s="120"/>
-      <c r="BF44" s="40"/>
-    </row>
-    <row r="45" spans="1:58" ht="30" customHeight="1" thickBot="1">
-      <c r="A45" s="104"/>
-      <c r="B45" s="105"/>
-      <c r="C45" s="105"/>
-      <c r="D45" s="105"/>
-      <c r="E45" s="105"/>
-      <c r="F45" s="105"/>
-      <c r="G45" s="105"/>
-      <c r="H45" s="105"/>
-      <c r="I45" s="105"/>
-      <c r="J45" s="105"/>
-      <c r="K45" s="105"/>
-      <c r="L45" s="105"/>
-      <c r="M45" s="105"/>
-      <c r="N45" s="105"/>
-      <c r="O45" s="105"/>
-      <c r="P45" s="105"/>
-      <c r="Q45" s="106"/>
-      <c r="R45" s="113"/>
-      <c r="S45" s="113"/>
-      <c r="T45" s="113"/>
-      <c r="U45" s="113"/>
-      <c r="V45" s="113"/>
-      <c r="W45" s="113"/>
-      <c r="X45" s="113"/>
-      <c r="Y45" s="113"/>
-      <c r="Z45" s="113"/>
-      <c r="AA45" s="113"/>
-      <c r="AB45" s="113"/>
-      <c r="AC45" s="113"/>
-      <c r="AD45" s="113"/>
-      <c r="AE45" s="113"/>
-      <c r="AF45" s="113"/>
-      <c r="AG45" s="113"/>
-      <c r="AH45" s="113"/>
-      <c r="AI45" s="113"/>
-      <c r="AJ45" s="113"/>
-      <c r="AK45" s="113"/>
-      <c r="AL45" s="113"/>
-      <c r="AM45" s="113"/>
-      <c r="AN45" s="113"/>
-      <c r="AO45" s="113"/>
-      <c r="AP45" s="113"/>
-      <c r="AQ45" s="113"/>
-      <c r="AR45" s="113"/>
-      <c r="AS45" s="113"/>
-      <c r="AT45" s="113"/>
-      <c r="AU45" s="114"/>
-      <c r="AV45" s="121"/>
-      <c r="AW45" s="122"/>
-      <c r="AX45" s="122"/>
-      <c r="AY45" s="122"/>
-      <c r="AZ45" s="122"/>
-      <c r="BA45" s="122"/>
-      <c r="BB45" s="122"/>
-      <c r="BC45" s="123"/>
-    </row>
-    <row r="46" spans="1:58">
+      <c r="S43" s="104"/>
+      <c r="T43" s="104"/>
+      <c r="U43" s="104"/>
+      <c r="V43" s="104"/>
+      <c r="W43" s="104"/>
+      <c r="X43" s="104"/>
+      <c r="Y43" s="104"/>
+      <c r="Z43" s="104"/>
+      <c r="AA43" s="104"/>
+      <c r="AB43" s="104"/>
+      <c r="AC43" s="104"/>
+      <c r="AD43" s="104"/>
+      <c r="AE43" s="104"/>
+      <c r="AF43" s="104"/>
+      <c r="AG43" s="104"/>
+      <c r="AH43" s="104"/>
+      <c r="AI43" s="104"/>
+      <c r="AJ43" s="104"/>
+      <c r="AK43" s="104"/>
+      <c r="AL43" s="104"/>
+      <c r="AM43" s="104"/>
+      <c r="AN43" s="104"/>
+      <c r="AO43" s="104"/>
+      <c r="AP43" s="104"/>
+      <c r="AQ43" s="104"/>
+      <c r="AR43" s="104"/>
+      <c r="AS43" s="104"/>
+      <c r="AT43" s="104"/>
+      <c r="AU43" s="105"/>
+      <c r="AV43" s="60"/>
+      <c r="AW43" s="61"/>
+      <c r="AX43" s="61"/>
+      <c r="AY43" s="61"/>
+      <c r="AZ43" s="61"/>
+      <c r="BA43" s="61"/>
+      <c r="BB43" s="61"/>
+      <c r="BC43" s="62"/>
+      <c r="BF43" s="39"/>
+    </row>
+    <row r="44" spans="1:60" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A44" s="86"/>
+      <c r="B44" s="87"/>
+      <c r="C44" s="87"/>
+      <c r="D44" s="87"/>
+      <c r="E44" s="87"/>
+      <c r="F44" s="87"/>
+      <c r="G44" s="87"/>
+      <c r="H44" s="87"/>
+      <c r="I44" s="87"/>
+      <c r="J44" s="87"/>
+      <c r="K44" s="87"/>
+      <c r="L44" s="87"/>
+      <c r="M44" s="87"/>
+      <c r="N44" s="87"/>
+      <c r="O44" s="87"/>
+      <c r="P44" s="87"/>
+      <c r="Q44" s="88"/>
+      <c r="R44" s="106"/>
+      <c r="S44" s="106"/>
+      <c r="T44" s="106"/>
+      <c r="U44" s="106"/>
+      <c r="V44" s="106"/>
+      <c r="W44" s="106"/>
+      <c r="X44" s="106"/>
+      <c r="Y44" s="106"/>
+      <c r="Z44" s="106"/>
+      <c r="AA44" s="106"/>
+      <c r="AB44" s="106"/>
+      <c r="AC44" s="106"/>
+      <c r="AD44" s="106"/>
+      <c r="AE44" s="106"/>
+      <c r="AF44" s="106"/>
+      <c r="AG44" s="106"/>
+      <c r="AH44" s="106"/>
+      <c r="AI44" s="106"/>
+      <c r="AJ44" s="106"/>
+      <c r="AK44" s="106"/>
+      <c r="AL44" s="106"/>
+      <c r="AM44" s="106"/>
+      <c r="AN44" s="106"/>
+      <c r="AO44" s="106"/>
+      <c r="AP44" s="106"/>
+      <c r="AQ44" s="106"/>
+      <c r="AR44" s="106"/>
+      <c r="AS44" s="106"/>
+      <c r="AT44" s="106"/>
+      <c r="AU44" s="107"/>
+      <c r="AV44" s="60"/>
+      <c r="AW44" s="61"/>
+      <c r="AX44" s="61"/>
+      <c r="AY44" s="61"/>
+      <c r="AZ44" s="61"/>
+      <c r="BA44" s="61"/>
+      <c r="BB44" s="61"/>
+      <c r="BC44" s="62"/>
+      <c r="BF44" s="39"/>
+    </row>
+    <row r="45" spans="1:60" ht="30" customHeight="1" thickBot="1">
+      <c r="A45" s="89"/>
+      <c r="B45" s="90"/>
+      <c r="C45" s="90"/>
+      <c r="D45" s="90"/>
+      <c r="E45" s="90"/>
+      <c r="F45" s="90"/>
+      <c r="G45" s="90"/>
+      <c r="H45" s="90"/>
+      <c r="I45" s="90"/>
+      <c r="J45" s="90"/>
+      <c r="K45" s="90"/>
+      <c r="L45" s="90"/>
+      <c r="M45" s="90"/>
+      <c r="N45" s="90"/>
+      <c r="O45" s="90"/>
+      <c r="P45" s="90"/>
+      <c r="Q45" s="91"/>
+      <c r="R45" s="108"/>
+      <c r="S45" s="108"/>
+      <c r="T45" s="108"/>
+      <c r="U45" s="108"/>
+      <c r="V45" s="108"/>
+      <c r="W45" s="108"/>
+      <c r="X45" s="108"/>
+      <c r="Y45" s="108"/>
+      <c r="Z45" s="108"/>
+      <c r="AA45" s="108"/>
+      <c r="AB45" s="108"/>
+      <c r="AC45" s="108"/>
+      <c r="AD45" s="108"/>
+      <c r="AE45" s="108"/>
+      <c r="AF45" s="108"/>
+      <c r="AG45" s="108"/>
+      <c r="AH45" s="108"/>
+      <c r="AI45" s="108"/>
+      <c r="AJ45" s="108"/>
+      <c r="AK45" s="108"/>
+      <c r="AL45" s="108"/>
+      <c r="AM45" s="108"/>
+      <c r="AN45" s="108"/>
+      <c r="AO45" s="108"/>
+      <c r="AP45" s="108"/>
+      <c r="AQ45" s="108"/>
+      <c r="AR45" s="108"/>
+      <c r="AS45" s="108"/>
+      <c r="AT45" s="108"/>
+      <c r="AU45" s="109"/>
+      <c r="AV45" s="63"/>
+      <c r="AW45" s="64"/>
+      <c r="AX45" s="64"/>
+      <c r="AY45" s="64"/>
+      <c r="AZ45" s="64"/>
+      <c r="BA45" s="64"/>
+      <c r="BB45" s="64"/>
+      <c r="BC45" s="65"/>
+    </row>
+    <row r="46" spans="1:60">
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -9242,7 +9867,7 @@
       <c r="AD46" s="1"/>
       <c r="AE46" s="1"/>
     </row>
-    <row r="47" spans="1:58">
+    <row r="47" spans="1:60">
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -9274,7 +9899,7 @@
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
     </row>
-    <row r="48" spans="1:58">
+    <row r="48" spans="1:60">
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -10491,16 +11116,50 @@
       <c r="AE85" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="66">
-    <mergeCell ref="AX7:AY8"/>
-    <mergeCell ref="AZ7:BA8"/>
-    <mergeCell ref="BB7:BC8"/>
-    <mergeCell ref="AJ7:AK8"/>
-    <mergeCell ref="AL7:AM8"/>
-    <mergeCell ref="AN7:AO8"/>
-    <mergeCell ref="AP7:AQ8"/>
-    <mergeCell ref="AV7:AW8"/>
-    <mergeCell ref="AT7:AU8"/>
+  <mergeCells count="68">
+    <mergeCell ref="BD7:BH7"/>
+    <mergeCell ref="BD6:BH6"/>
+    <mergeCell ref="G2:AW3"/>
+    <mergeCell ref="AF7:AG8"/>
+    <mergeCell ref="AH7:AI8"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="R7:S8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="A6:B9"/>
+    <mergeCell ref="A10:A21"/>
+    <mergeCell ref="AD7:AE8"/>
+    <mergeCell ref="X7:Y8"/>
+    <mergeCell ref="Z7:AA8"/>
+    <mergeCell ref="A22:A33"/>
+    <mergeCell ref="T7:U8"/>
+    <mergeCell ref="V7:W8"/>
+    <mergeCell ref="AB7:AC8"/>
+    <mergeCell ref="AF42:AG42"/>
+    <mergeCell ref="AH37:AU42"/>
+    <mergeCell ref="A34:Q34"/>
+    <mergeCell ref="AF35:AG36"/>
+    <mergeCell ref="AH35:AU36"/>
+    <mergeCell ref="AF37:AG37"/>
+    <mergeCell ref="AF38:AG38"/>
+    <mergeCell ref="AF39:AG39"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="C35:Q36"/>
+    <mergeCell ref="A43:Q45"/>
+    <mergeCell ref="R35:S36"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C38:Q38"/>
+    <mergeCell ref="C39:Q39"/>
+    <mergeCell ref="C40:Q40"/>
+    <mergeCell ref="C41:Q41"/>
+    <mergeCell ref="C42:Q42"/>
+    <mergeCell ref="R43:AU45"/>
+    <mergeCell ref="AF40:AG40"/>
+    <mergeCell ref="AF41:AG41"/>
     <mergeCell ref="AV37:BC45"/>
     <mergeCell ref="R34:AU34"/>
     <mergeCell ref="AV34:BC36"/>
@@ -10517,47 +11176,15 @@
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="AR7:AS8"/>
-    <mergeCell ref="A43:Q45"/>
-    <mergeCell ref="R35:S36"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C38:Q38"/>
-    <mergeCell ref="C39:Q39"/>
-    <mergeCell ref="C40:Q40"/>
-    <mergeCell ref="C41:Q41"/>
-    <mergeCell ref="C42:Q42"/>
-    <mergeCell ref="R43:AU45"/>
-    <mergeCell ref="AF40:AG40"/>
-    <mergeCell ref="AF41:AG41"/>
-    <mergeCell ref="AF42:AG42"/>
-    <mergeCell ref="AH37:AU42"/>
-    <mergeCell ref="A34:Q34"/>
-    <mergeCell ref="AF35:AG36"/>
-    <mergeCell ref="AH35:AU36"/>
-    <mergeCell ref="AF37:AG37"/>
-    <mergeCell ref="AF38:AG38"/>
-    <mergeCell ref="AF39:AG39"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="C35:Q36"/>
-    <mergeCell ref="G2:AW3"/>
-    <mergeCell ref="AF7:AG8"/>
-    <mergeCell ref="AH7:AI8"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="R7:S8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="A6:B9"/>
-    <mergeCell ref="A10:A21"/>
-    <mergeCell ref="AD7:AE8"/>
-    <mergeCell ref="X7:Y8"/>
-    <mergeCell ref="Z7:AA8"/>
-    <mergeCell ref="A22:A33"/>
-    <mergeCell ref="T7:U8"/>
-    <mergeCell ref="V7:W8"/>
-    <mergeCell ref="AB7:AC8"/>
+    <mergeCell ref="AX7:AY8"/>
+    <mergeCell ref="AZ7:BA8"/>
+    <mergeCell ref="BB7:BC8"/>
+    <mergeCell ref="AJ7:AK8"/>
+    <mergeCell ref="AL7:AM8"/>
+    <mergeCell ref="AN7:AO8"/>
+    <mergeCell ref="AP7:AQ8"/>
+    <mergeCell ref="AV7:AW8"/>
+    <mergeCell ref="AT7:AU8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094499" right="0.196850393700787" top="0.39370078740157499" bottom="0.35433070866141703" header="0.39370078740157499" footer="0.35433070866141703"/>
@@ -10571,7 +11198,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{193167E0-CA48-4A1C-AB54-F77183DD24F0}">
-  <dimension ref="A1:AA58"/>
+  <dimension ref="A1:AA63"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18.25" customWidth="1"/>
@@ -10580,1955 +11207,2123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" s="147"/>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="148" t="s">
+      <c r="A1" s="148"/>
+      <c r="B1" s="148"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="149" t="s">
         <v>124</v>
       </c>
-      <c r="S1" s="148"/>
-      <c r="T1" s="148"/>
-      <c r="U1" s="148"/>
+      <c r="S1" s="149"/>
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="147"/>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="149" t="s">
+      <c r="A2" s="148"/>
+      <c r="B2" s="148"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="150" t="s">
         <v>139</v>
       </c>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
-      <c r="M2" s="149"/>
-      <c r="N2" s="149"/>
-      <c r="O2" s="149"/>
-      <c r="P2" s="149"/>
-      <c r="Q2" s="149"/>
-      <c r="R2" s="150" t="s">
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="150"/>
+      <c r="M2" s="150"/>
+      <c r="N2" s="150"/>
+      <c r="O2" s="150"/>
+      <c r="P2" s="150"/>
+      <c r="Q2" s="150"/>
+      <c r="R2" s="151" t="s">
         <v>125</v>
       </c>
-      <c r="S2" s="150"/>
-      <c r="T2" s="150"/>
-      <c r="U2" s="150"/>
+      <c r="S2" s="151"/>
+      <c r="T2" s="151"/>
+      <c r="U2" s="151"/>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="147"/>
-      <c r="B3" s="147"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="149"/>
-      <c r="F3" s="149"/>
-      <c r="G3" s="149"/>
-      <c r="H3" s="149"/>
-      <c r="I3" s="149"/>
-      <c r="J3" s="149"/>
-      <c r="K3" s="149"/>
-      <c r="L3" s="149"/>
-      <c r="M3" s="149"/>
-      <c r="N3" s="149"/>
-      <c r="O3" s="149"/>
-      <c r="P3" s="149"/>
-      <c r="Q3" s="149"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="41"/>
-      <c r="U3" s="41"/>
+      <c r="A3" s="148"/>
+      <c r="B3" s="148"/>
+      <c r="C3" s="148"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="150"/>
+      <c r="F3" s="150"/>
+      <c r="G3" s="150"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="150"/>
+      <c r="K3" s="150"/>
+      <c r="L3" s="150"/>
+      <c r="M3" s="150"/>
+      <c r="N3" s="150"/>
+      <c r="O3" s="150"/>
+      <c r="P3" s="150"/>
+      <c r="Q3" s="150"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="42"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="43" t="s">
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="S4" s="43"/>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
+      <c r="S4" s="42"/>
+      <c r="T4" s="42"/>
+      <c r="U4" s="42"/>
     </row>
     <row r="5" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A5" s="151" t="s">
+      <c r="A5" s="152" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="152"/>
-      <c r="C5" s="44" t="s">
+      <c r="B5" s="153"/>
+      <c r="C5" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="49">
+      <c r="D5" s="48">
         <v>0.33333333333333331</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="48">
         <v>0.375</v>
       </c>
-      <c r="F5" s="49">
+      <c r="F5" s="48">
         <v>0.41666666666666669</v>
       </c>
-      <c r="G5" s="49">
+      <c r="G5" s="48">
         <v>0.45833333333333331</v>
       </c>
-      <c r="H5" s="49">
+      <c r="H5" s="48">
         <v>0.5</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="48">
         <v>0.54166666666666663</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="48">
         <v>0.58333333333333337</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="48">
         <v>0.625</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="48">
         <v>0.66666666666666663</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="48">
         <v>0.70833333333333337</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="48">
         <v>0.75</v>
       </c>
-      <c r="O5" s="49">
+      <c r="O5" s="48">
         <v>0.79166666666666663</v>
       </c>
-      <c r="P5" s="49">
+      <c r="P5" s="48">
         <v>0.83333333333333337</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="48">
         <v>0.875</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="48">
         <v>0.91666666666666663</v>
       </c>
-      <c r="S5" s="49">
+      <c r="S5" s="48">
         <v>0.95833333333333337</v>
       </c>
-      <c r="T5" s="49">
-        <v>0</v>
-      </c>
-      <c r="U5" s="49">
+      <c r="T5" s="48">
+        <v>0</v>
+      </c>
+      <c r="U5" s="48">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="V5" s="49">
+      <c r="V5" s="48">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="W5" s="49">
+      <c r="W5" s="48">
         <v>0.125</v>
       </c>
-      <c r="X5" s="49">
+      <c r="X5" s="48">
         <v>0.16666666666666666</v>
       </c>
-      <c r="Y5" s="49">
+      <c r="Y5" s="48">
         <v>0.20833333333333334</v>
       </c>
-      <c r="Z5" s="49">
+      <c r="Z5" s="48">
         <v>0.25</v>
       </c>
-      <c r="AA5" s="49">
+      <c r="AA5" s="48">
         <v>0.29166666666666669</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="15.75">
-      <c r="A6" s="153" t="s">
+      <c r="A6" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="154"/>
-      <c r="C6" s="48" t="s">
+      <c r="B6" s="143"/>
+      <c r="C6" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="45"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="45"/>
-      <c r="U6" s="45"/>
-      <c r="V6" s="45"/>
-      <c r="W6" s="45"/>
-      <c r="X6" s="45"/>
-      <c r="Y6" s="45"/>
-      <c r="Z6" s="45"/>
-      <c r="AA6" s="45"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="44"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="44"/>
+      <c r="U6" s="44"/>
+      <c r="V6" s="44"/>
+      <c r="W6" s="44"/>
+      <c r="X6" s="44"/>
+      <c r="Y6" s="44"/>
+      <c r="Z6" s="44"/>
+      <c r="AA6" s="44"/>
     </row>
     <row r="7" spans="1:27" ht="15.75">
-      <c r="A7" s="153" t="s">
+      <c r="A7" s="142" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="154"/>
-      <c r="C7" s="48" t="s">
+      <c r="B7" s="143"/>
+      <c r="C7" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="45"/>
-      <c r="R7" s="45"/>
-      <c r="S7" s="45"/>
-      <c r="T7" s="45"/>
-      <c r="U7" s="45"/>
-      <c r="V7" s="45"/>
-      <c r="W7" s="45"/>
-      <c r="X7" s="45"/>
-      <c r="Y7" s="45"/>
-      <c r="Z7" s="45"/>
-      <c r="AA7" s="45"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="44"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="44"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="44"/>
+      <c r="U7" s="44"/>
+      <c r="V7" s="44"/>
+      <c r="W7" s="44"/>
+      <c r="X7" s="44"/>
+      <c r="Y7" s="44"/>
+      <c r="Z7" s="44"/>
+      <c r="AA7" s="44"/>
     </row>
     <row r="8" spans="1:27" ht="15.75">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="45"/>
-      <c r="N8" s="45"/>
-      <c r="O8" s="45"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" s="45"/>
-      <c r="R8" s="45"/>
-      <c r="S8" s="45"/>
-      <c r="T8" s="45"/>
-      <c r="U8" s="45"/>
-      <c r="V8" s="45"/>
-      <c r="W8" s="45"/>
-      <c r="X8" s="45"/>
-      <c r="Y8" s="45"/>
-      <c r="Z8" s="45"/>
-      <c r="AA8" s="45"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="44"/>
+      <c r="N8" s="44"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="44"/>
+      <c r="Q8" s="44"/>
+      <c r="R8" s="44"/>
+      <c r="S8" s="44"/>
+      <c r="T8" s="44"/>
+      <c r="U8" s="44"/>
+      <c r="V8" s="44"/>
+      <c r="W8" s="44"/>
+      <c r="X8" s="44"/>
+      <c r="Y8" s="44"/>
+      <c r="Z8" s="44"/>
+      <c r="AA8" s="44"/>
     </row>
     <row r="9" spans="1:27" ht="15.75">
-      <c r="A9" s="155" t="s">
+      <c r="A9" s="144" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="45"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="45"/>
-      <c r="O9" s="45"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" s="45"/>
-      <c r="R9" s="45"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="45"/>
-      <c r="U9" s="45"/>
-      <c r="V9" s="45"/>
-      <c r="W9" s="45"/>
-      <c r="X9" s="45"/>
-      <c r="Y9" s="45"/>
-      <c r="Z9" s="45"/>
-      <c r="AA9" s="45"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="44"/>
+      <c r="M9" s="44"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="44"/>
+      <c r="P9" s="44"/>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="44"/>
+      <c r="S9" s="44"/>
+      <c r="T9" s="44"/>
+      <c r="U9" s="44"/>
+      <c r="V9" s="44"/>
+      <c r="W9" s="44"/>
+      <c r="X9" s="44"/>
+      <c r="Y9" s="44"/>
+      <c r="Z9" s="44"/>
+      <c r="AA9" s="44"/>
     </row>
     <row r="10" spans="1:27" ht="15.75">
-      <c r="A10" s="156"/>
-      <c r="B10" s="47" t="s">
+      <c r="A10" s="145"/>
+      <c r="B10" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="45"/>
-      <c r="M10" s="45"/>
-      <c r="N10" s="45"/>
-      <c r="O10" s="45"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="45"/>
-      <c r="S10" s="45"/>
-      <c r="T10" s="45"/>
-      <c r="U10" s="45"/>
-      <c r="V10" s="45"/>
-      <c r="W10" s="45"/>
-      <c r="X10" s="45"/>
-      <c r="Y10" s="45"/>
-      <c r="Z10" s="45"/>
-      <c r="AA10" s="45"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
+      <c r="N10" s="44"/>
+      <c r="O10" s="44"/>
+      <c r="P10" s="44"/>
+      <c r="Q10" s="44"/>
+      <c r="R10" s="44"/>
+      <c r="S10" s="44"/>
+      <c r="T10" s="44"/>
+      <c r="U10" s="44"/>
+      <c r="V10" s="44"/>
+      <c r="W10" s="44"/>
+      <c r="X10" s="44"/>
+      <c r="Y10" s="44"/>
+      <c r="Z10" s="44"/>
+      <c r="AA10" s="44"/>
     </row>
     <row r="11" spans="1:27" ht="15.75">
-      <c r="A11" s="155" t="s">
+      <c r="A11" s="144" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="45"/>
-      <c r="M11" s="45"/>
-      <c r="N11" s="45"/>
-      <c r="O11" s="45"/>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="45"/>
-      <c r="R11" s="45"/>
-      <c r="S11" s="45"/>
-      <c r="T11" s="45"/>
-      <c r="U11" s="45"/>
-      <c r="V11" s="45"/>
-      <c r="W11" s="45"/>
-      <c r="X11" s="45"/>
-      <c r="Y11" s="45"/>
-      <c r="Z11" s="45"/>
-      <c r="AA11" s="45"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="44"/>
+      <c r="W11" s="44"/>
+      <c r="X11" s="44"/>
+      <c r="Y11" s="44"/>
+      <c r="Z11" s="44"/>
+      <c r="AA11" s="44"/>
     </row>
     <row r="12" spans="1:27" ht="15.75">
-      <c r="A12" s="157"/>
-      <c r="B12" s="47" t="s">
+      <c r="A12" s="146"/>
+      <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45"/>
-      <c r="N12" s="45"/>
-      <c r="O12" s="45"/>
-      <c r="P12" s="45"/>
-      <c r="Q12" s="45"/>
-      <c r="R12" s="45"/>
-      <c r="S12" s="45"/>
-      <c r="T12" s="45"/>
-      <c r="U12" s="45"/>
-      <c r="V12" s="45"/>
-      <c r="W12" s="45"/>
-      <c r="X12" s="45"/>
-      <c r="Y12" s="45"/>
-      <c r="Z12" s="45"/>
-      <c r="AA12" s="45"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
+      <c r="T12" s="44"/>
+      <c r="U12" s="44"/>
+      <c r="V12" s="44"/>
+      <c r="W12" s="44"/>
+      <c r="X12" s="44"/>
+      <c r="Y12" s="44"/>
+      <c r="Z12" s="44"/>
+      <c r="AA12" s="44"/>
     </row>
     <row r="13" spans="1:27" ht="15.75">
-      <c r="A13" s="157"/>
-      <c r="B13" s="47" t="s">
+      <c r="A13" s="146"/>
+      <c r="B13" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="45"/>
-      <c r="M13" s="45"/>
-      <c r="N13" s="45"/>
-      <c r="O13" s="45"/>
-      <c r="P13" s="45"/>
-      <c r="Q13" s="45"/>
-      <c r="R13" s="45"/>
-      <c r="S13" s="45"/>
-      <c r="T13" s="45"/>
-      <c r="U13" s="45"/>
-      <c r="V13" s="45"/>
-      <c r="W13" s="45"/>
-      <c r="X13" s="45"/>
-      <c r="Y13" s="45"/>
-      <c r="Z13" s="45"/>
-      <c r="AA13" s="45"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="44"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="44"/>
+      <c r="U13" s="44"/>
+      <c r="V13" s="44"/>
+      <c r="W13" s="44"/>
+      <c r="X13" s="44"/>
+      <c r="Y13" s="44"/>
+      <c r="Z13" s="44"/>
+      <c r="AA13" s="44"/>
     </row>
     <row r="14" spans="1:27" ht="15.75">
-      <c r="A14" s="157"/>
-      <c r="B14" s="47" t="s">
+      <c r="A14" s="146"/>
+      <c r="B14" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="45"/>
-      <c r="L14" s="45"/>
-      <c r="M14" s="45"/>
-      <c r="N14" s="45"/>
-      <c r="O14" s="45"/>
-      <c r="P14" s="45"/>
-      <c r="Q14" s="45"/>
-      <c r="R14" s="45"/>
-      <c r="S14" s="45"/>
-      <c r="T14" s="45"/>
-      <c r="U14" s="45"/>
-      <c r="V14" s="45"/>
-      <c r="W14" s="45"/>
-      <c r="X14" s="45"/>
-      <c r="Y14" s="45"/>
-      <c r="Z14" s="45"/>
-      <c r="AA14" s="45"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="44"/>
+      <c r="P14" s="44"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="44"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="44"/>
+      <c r="U14" s="44"/>
+      <c r="V14" s="44"/>
+      <c r="W14" s="44"/>
+      <c r="X14" s="44"/>
+      <c r="Y14" s="44"/>
+      <c r="Z14" s="44"/>
+      <c r="AA14" s="44"/>
     </row>
     <row r="15" spans="1:27" ht="15.75">
-      <c r="A15" s="157"/>
-      <c r="B15" s="47" t="s">
+      <c r="A15" s="146"/>
+      <c r="B15" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="48" t="s">
+      <c r="C15" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45"/>
-      <c r="M15" s="45"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="45"/>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="45"/>
-      <c r="S15" s="45"/>
-      <c r="T15" s="45"/>
-      <c r="U15" s="45"/>
-      <c r="V15" s="45"/>
-      <c r="W15" s="45"/>
-      <c r="X15" s="45"/>
-      <c r="Y15" s="45"/>
-      <c r="Z15" s="45"/>
-      <c r="AA15" s="45"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="44"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="44"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="44"/>
+      <c r="U15" s="44"/>
+      <c r="V15" s="44"/>
+      <c r="W15" s="44"/>
+      <c r="X15" s="44"/>
+      <c r="Y15" s="44"/>
+      <c r="Z15" s="44"/>
+      <c r="AA15" s="44"/>
     </row>
     <row r="16" spans="1:27" ht="15.75">
-      <c r="A16" s="157"/>
-      <c r="B16" s="47" t="s">
+      <c r="A16" s="146"/>
+      <c r="B16" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="45"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="45"/>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="45"/>
-      <c r="R16" s="45"/>
-      <c r="S16" s="45"/>
-      <c r="T16" s="45"/>
-      <c r="U16" s="45"/>
-      <c r="V16" s="45"/>
-      <c r="W16" s="45"/>
-      <c r="X16" s="45"/>
-      <c r="Y16" s="45"/>
-      <c r="Z16" s="45"/>
-      <c r="AA16" s="45"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="44"/>
+      <c r="M16" s="44"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="44"/>
+      <c r="S16" s="44"/>
+      <c r="T16" s="44"/>
+      <c r="U16" s="44"/>
+      <c r="V16" s="44"/>
+      <c r="W16" s="44"/>
+      <c r="X16" s="44"/>
+      <c r="Y16" s="44"/>
+      <c r="Z16" s="44"/>
+      <c r="AA16" s="44"/>
     </row>
     <row r="17" spans="1:27" ht="15.75">
-      <c r="A17" s="157"/>
-      <c r="B17" s="47" t="s">
+      <c r="A17" s="146"/>
+      <c r="B17" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="C17" s="48" t="s">
+      <c r="C17" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="45"/>
-      <c r="M17" s="45"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="45"/>
-      <c r="P17" s="45"/>
-      <c r="Q17" s="45"/>
-      <c r="R17" s="45"/>
-      <c r="S17" s="45"/>
-      <c r="T17" s="45"/>
-      <c r="U17" s="45"/>
-      <c r="V17" s="45"/>
-      <c r="W17" s="45"/>
-      <c r="X17" s="45"/>
-      <c r="Y17" s="45"/>
-      <c r="Z17" s="45"/>
-      <c r="AA17" s="45"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44"/>
+      <c r="L17" s="44"/>
+      <c r="M17" s="44"/>
+      <c r="N17" s="44"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="44"/>
+      <c r="S17" s="44"/>
+      <c r="T17" s="44"/>
+      <c r="U17" s="44"/>
+      <c r="V17" s="44"/>
+      <c r="W17" s="44"/>
+      <c r="X17" s="44"/>
+      <c r="Y17" s="44"/>
+      <c r="Z17" s="44"/>
+      <c r="AA17" s="44"/>
     </row>
     <row r="18" spans="1:27" ht="15.75">
-      <c r="A18" s="157"/>
-      <c r="B18" s="47" t="s">
+      <c r="A18" s="146"/>
+      <c r="B18" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="45"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="45"/>
-      <c r="R18" s="45"/>
-      <c r="S18" s="45"/>
-      <c r="T18" s="45"/>
-      <c r="U18" s="45"/>
-      <c r="V18" s="45"/>
-      <c r="W18" s="45"/>
-      <c r="X18" s="45"/>
-      <c r="Y18" s="45"/>
-      <c r="Z18" s="45"/>
-      <c r="AA18" s="45"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="44"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="44"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="44"/>
+      <c r="R18" s="44"/>
+      <c r="S18" s="44"/>
+      <c r="T18" s="44"/>
+      <c r="U18" s="44"/>
+      <c r="V18" s="44"/>
+      <c r="W18" s="44"/>
+      <c r="X18" s="44"/>
+      <c r="Y18" s="44"/>
+      <c r="Z18" s="44"/>
+      <c r="AA18" s="44"/>
     </row>
     <row r="19" spans="1:27" ht="15.75">
-      <c r="A19" s="157"/>
-      <c r="B19" s="47" t="s">
+      <c r="A19" s="146"/>
+      <c r="B19" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C19" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="45"/>
-      <c r="M19" s="45"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="45"/>
-      <c r="P19" s="45"/>
-      <c r="Q19" s="45"/>
-      <c r="R19" s="45"/>
-      <c r="S19" s="45"/>
-      <c r="T19" s="45"/>
-      <c r="U19" s="45"/>
-      <c r="V19" s="45"/>
-      <c r="W19" s="45"/>
-      <c r="X19" s="45"/>
-      <c r="Y19" s="45"/>
-      <c r="Z19" s="45"/>
-      <c r="AA19" s="45"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="44"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="44"/>
+      <c r="S19" s="44"/>
+      <c r="T19" s="44"/>
+      <c r="U19" s="44"/>
+      <c r="V19" s="44"/>
+      <c r="W19" s="44"/>
+      <c r="X19" s="44"/>
+      <c r="Y19" s="44"/>
+      <c r="Z19" s="44"/>
+      <c r="AA19" s="44"/>
     </row>
     <row r="20" spans="1:27" ht="15.75">
-      <c r="A20" s="157"/>
-      <c r="B20" s="47" t="s">
+      <c r="A20" s="146"/>
+      <c r="B20" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="C20" s="48" t="s">
+      <c r="C20" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="45"/>
-      <c r="M20" s="45"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="45"/>
-      <c r="P20" s="45"/>
-      <c r="Q20" s="45"/>
-      <c r="R20" s="45"/>
-      <c r="S20" s="45"/>
-      <c r="T20" s="45"/>
-      <c r="U20" s="45"/>
-      <c r="V20" s="45"/>
-      <c r="W20" s="45"/>
-      <c r="X20" s="45"/>
-      <c r="Y20" s="45"/>
-      <c r="Z20" s="45"/>
-      <c r="AA20" s="45"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="44"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="44"/>
+      <c r="O20" s="44"/>
+      <c r="P20" s="44"/>
+      <c r="Q20" s="44"/>
+      <c r="R20" s="44"/>
+      <c r="S20" s="44"/>
+      <c r="T20" s="44"/>
+      <c r="U20" s="44"/>
+      <c r="V20" s="44"/>
+      <c r="W20" s="44"/>
+      <c r="X20" s="44"/>
+      <c r="Y20" s="44"/>
+      <c r="Z20" s="44"/>
+      <c r="AA20" s="44"/>
     </row>
     <row r="21" spans="1:27" ht="15.75">
-      <c r="A21" s="157"/>
-      <c r="B21" s="47" t="s">
+      <c r="A21" s="146"/>
+      <c r="B21" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="C21" s="48" t="s">
+      <c r="C21" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="45"/>
-      <c r="M21" s="45"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="45"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" s="45"/>
-      <c r="R21" s="45"/>
-      <c r="S21" s="45"/>
-      <c r="T21" s="45"/>
-      <c r="U21" s="45"/>
-      <c r="V21" s="45"/>
-      <c r="W21" s="45"/>
-      <c r="X21" s="45"/>
-      <c r="Y21" s="45"/>
-      <c r="Z21" s="45"/>
-      <c r="AA21" s="45"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="44"/>
+      <c r="R21" s="44"/>
+      <c r="S21" s="44"/>
+      <c r="T21" s="44"/>
+      <c r="U21" s="44"/>
+      <c r="V21" s="44"/>
+      <c r="W21" s="44"/>
+      <c r="X21" s="44"/>
+      <c r="Y21" s="44"/>
+      <c r="Z21" s="44"/>
+      <c r="AA21" s="44"/>
     </row>
     <row r="22" spans="1:27" ht="15.75">
-      <c r="A22" s="157"/>
-      <c r="B22" s="47" t="s">
+      <c r="A22" s="146"/>
+      <c r="B22" s="46" t="s">
         <v>136</v>
       </c>
-      <c r="C22" s="48" t="s">
+      <c r="C22" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="45"/>
-      <c r="M22" s="45"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="45"/>
-      <c r="P22" s="45"/>
-      <c r="Q22" s="45"/>
-      <c r="R22" s="45"/>
-      <c r="S22" s="45"/>
-      <c r="T22" s="45"/>
-      <c r="U22" s="45"/>
-      <c r="V22" s="45"/>
-      <c r="W22" s="45"/>
-      <c r="X22" s="45"/>
-      <c r="Y22" s="45"/>
-      <c r="Z22" s="45"/>
-      <c r="AA22" s="45"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="44"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="44"/>
+      <c r="P22" s="44"/>
+      <c r="Q22" s="44"/>
+      <c r="R22" s="44"/>
+      <c r="S22" s="44"/>
+      <c r="T22" s="44"/>
+      <c r="U22" s="44"/>
+      <c r="V22" s="44"/>
+      <c r="W22" s="44"/>
+      <c r="X22" s="44"/>
+      <c r="Y22" s="44"/>
+      <c r="Z22" s="44"/>
+      <c r="AA22" s="44"/>
     </row>
     <row r="23" spans="1:27" ht="15.75">
-      <c r="A23" s="157"/>
-      <c r="B23" s="47" t="s">
+      <c r="A23" s="146"/>
+      <c r="B23" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="48" t="s">
+      <c r="C23" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="45"/>
-      <c r="P23" s="45"/>
-      <c r="Q23" s="45"/>
-      <c r="R23" s="45"/>
-      <c r="S23" s="45"/>
-      <c r="T23" s="45"/>
-      <c r="U23" s="45"/>
-      <c r="V23" s="45"/>
-      <c r="W23" s="45"/>
-      <c r="X23" s="45"/>
-      <c r="Y23" s="45"/>
-      <c r="Z23" s="45"/>
-      <c r="AA23" s="45"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="44"/>
+      <c r="R23" s="44"/>
+      <c r="S23" s="44"/>
+      <c r="T23" s="44"/>
+      <c r="U23" s="44"/>
+      <c r="V23" s="44"/>
+      <c r="W23" s="44"/>
+      <c r="X23" s="44"/>
+      <c r="Y23" s="44"/>
+      <c r="Z23" s="44"/>
+      <c r="AA23" s="44"/>
     </row>
     <row r="24" spans="1:27" ht="15.75">
-      <c r="A24" s="157"/>
-      <c r="B24" s="47" t="s">
+      <c r="A24" s="146"/>
+      <c r="B24" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="48" t="s">
+      <c r="C24" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="45"/>
-      <c r="M24" s="45"/>
-      <c r="N24" s="45"/>
-      <c r="O24" s="45"/>
-      <c r="P24" s="45"/>
-      <c r="Q24" s="45"/>
-      <c r="R24" s="45"/>
-      <c r="S24" s="45"/>
-      <c r="T24" s="45"/>
-      <c r="U24" s="45"/>
-      <c r="V24" s="45"/>
-      <c r="W24" s="45"/>
-      <c r="X24" s="45"/>
-      <c r="Y24" s="45"/>
-      <c r="Z24" s="45"/>
-      <c r="AA24" s="45"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="44"/>
+      <c r="M24" s="44"/>
+      <c r="N24" s="44"/>
+      <c r="O24" s="44"/>
+      <c r="P24" s="44"/>
+      <c r="Q24" s="44"/>
+      <c r="R24" s="44"/>
+      <c r="S24" s="44"/>
+      <c r="T24" s="44"/>
+      <c r="U24" s="44"/>
+      <c r="V24" s="44"/>
+      <c r="W24" s="44"/>
+      <c r="X24" s="44"/>
+      <c r="Y24" s="44"/>
+      <c r="Z24" s="44"/>
+      <c r="AA24" s="44"/>
     </row>
     <row r="25" spans="1:27" ht="15.75">
-      <c r="A25" s="157"/>
-      <c r="B25" s="47" t="s">
+      <c r="A25" s="146"/>
+      <c r="B25" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="48" t="s">
+      <c r="C25" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="45"/>
-      <c r="M25" s="45"/>
-      <c r="N25" s="45"/>
-      <c r="O25" s="45"/>
-      <c r="P25" s="45"/>
-      <c r="Q25" s="45"/>
-      <c r="R25" s="45"/>
-      <c r="S25" s="45"/>
-      <c r="T25" s="45"/>
-      <c r="U25" s="45"/>
-      <c r="V25" s="45"/>
-      <c r="W25" s="45"/>
-      <c r="X25" s="45"/>
-      <c r="Y25" s="45"/>
-      <c r="Z25" s="45"/>
-      <c r="AA25" s="45"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
+      <c r="L25" s="44"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="44"/>
+      <c r="O25" s="44"/>
+      <c r="P25" s="44"/>
+      <c r="Q25" s="44"/>
+      <c r="R25" s="44"/>
+      <c r="S25" s="44"/>
+      <c r="T25" s="44"/>
+      <c r="U25" s="44"/>
+      <c r="V25" s="44"/>
+      <c r="W25" s="44"/>
+      <c r="X25" s="44"/>
+      <c r="Y25" s="44"/>
+      <c r="Z25" s="44"/>
+      <c r="AA25" s="44"/>
     </row>
     <row r="26" spans="1:27" ht="15.75">
-      <c r="A26" s="157"/>
-      <c r="B26" s="47" t="s">
+      <c r="A26" s="146"/>
+      <c r="B26" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="48" t="s">
+      <c r="C26" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="45"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="45"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="45"/>
-      <c r="R26" s="45"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="45"/>
-      <c r="U26" s="45"/>
-      <c r="V26" s="45"/>
-      <c r="W26" s="45"/>
-      <c r="X26" s="45"/>
-      <c r="Y26" s="45"/>
-      <c r="Z26" s="45"/>
-      <c r="AA26" s="45"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="44"/>
+      <c r="L26" s="44"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="44"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="44"/>
+      <c r="Q26" s="44"/>
+      <c r="R26" s="44"/>
+      <c r="S26" s="44"/>
+      <c r="T26" s="44"/>
+      <c r="U26" s="44"/>
+      <c r="V26" s="44"/>
+      <c r="W26" s="44"/>
+      <c r="X26" s="44"/>
+      <c r="Y26" s="44"/>
+      <c r="Z26" s="44"/>
+      <c r="AA26" s="44"/>
     </row>
     <row r="27" spans="1:27" ht="15.75">
-      <c r="A27" s="157"/>
-      <c r="B27" s="47" t="s">
+      <c r="A27" s="146"/>
+      <c r="B27" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="48" t="s">
+      <c r="C27" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="45"/>
-      <c r="M27" s="45"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="45"/>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="45"/>
-      <c r="R27" s="45"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="45"/>
-      <c r="U27" s="45"/>
-      <c r="V27" s="45"/>
-      <c r="W27" s="45"/>
-      <c r="X27" s="45"/>
-      <c r="Y27" s="45"/>
-      <c r="Z27" s="45"/>
-      <c r="AA27" s="45"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="44"/>
+      <c r="L27" s="44"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="44"/>
+      <c r="O27" s="44"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="44"/>
+      <c r="R27" s="44"/>
+      <c r="S27" s="44"/>
+      <c r="T27" s="44"/>
+      <c r="U27" s="44"/>
+      <c r="V27" s="44"/>
+      <c r="W27" s="44"/>
+      <c r="X27" s="44"/>
+      <c r="Y27" s="44"/>
+      <c r="Z27" s="44"/>
+      <c r="AA27" s="44"/>
     </row>
     <row r="28" spans="1:27" ht="15.75">
-      <c r="A28" s="157"/>
-      <c r="B28" s="47" t="s">
+      <c r="A28" s="146"/>
+      <c r="B28" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="48" t="s">
+      <c r="C28" s="47" t="s">
         <v>80</v>
       </c>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="45"/>
-      <c r="M28" s="45"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="45"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="45"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="45"/>
-      <c r="U28" s="45"/>
-      <c r="V28" s="45"/>
-      <c r="W28" s="45"/>
-      <c r="X28" s="45"/>
-      <c r="Y28" s="45"/>
-      <c r="Z28" s="45"/>
-      <c r="AA28" s="45"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="44"/>
+      <c r="L28" s="44"/>
+      <c r="M28" s="44"/>
+      <c r="N28" s="44"/>
+      <c r="O28" s="44"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="44"/>
+      <c r="S28" s="44"/>
+      <c r="T28" s="44"/>
+      <c r="U28" s="44"/>
+      <c r="V28" s="44"/>
+      <c r="W28" s="44"/>
+      <c r="X28" s="44"/>
+      <c r="Y28" s="44"/>
+      <c r="Z28" s="44"/>
+      <c r="AA28" s="44"/>
     </row>
     <row r="29" spans="1:27" ht="15.75">
-      <c r="A29" s="157"/>
-      <c r="B29" s="47" t="s">
+      <c r="A29" s="146"/>
+      <c r="B29" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="48" t="s">
+      <c r="C29" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="45"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="45"/>
-      <c r="M29" s="45"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="45"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="45"/>
-      <c r="R29" s="45"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="45"/>
-      <c r="U29" s="45"/>
-      <c r="V29" s="45"/>
-      <c r="W29" s="45"/>
-      <c r="X29" s="45"/>
-      <c r="Y29" s="45"/>
-      <c r="Z29" s="45"/>
-      <c r="AA29" s="45"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="44"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="44"/>
+      <c r="O29" s="44"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="44"/>
+      <c r="S29" s="44"/>
+      <c r="T29" s="44"/>
+      <c r="U29" s="44"/>
+      <c r="V29" s="44"/>
+      <c r="W29" s="44"/>
+      <c r="X29" s="44"/>
+      <c r="Y29" s="44"/>
+      <c r="Z29" s="44"/>
+      <c r="AA29" s="44"/>
     </row>
     <row r="30" spans="1:27" ht="15.75">
-      <c r="A30" s="157"/>
-      <c r="B30" s="47" t="s">
+      <c r="A30" s="146"/>
+      <c r="B30" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="48" t="s">
+      <c r="C30" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="45"/>
-      <c r="M30" s="45"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="45"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="45"/>
-      <c r="R30" s="45"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="45"/>
-      <c r="U30" s="45"/>
-      <c r="V30" s="45"/>
-      <c r="W30" s="45"/>
-      <c r="X30" s="45"/>
-      <c r="Y30" s="45"/>
-      <c r="Z30" s="45"/>
-      <c r="AA30" s="45"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
+      <c r="K30" s="44"/>
+      <c r="L30" s="44"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="44"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="44"/>
+      <c r="S30" s="44"/>
+      <c r="T30" s="44"/>
+      <c r="U30" s="44"/>
+      <c r="V30" s="44"/>
+      <c r="W30" s="44"/>
+      <c r="X30" s="44"/>
+      <c r="Y30" s="44"/>
+      <c r="Z30" s="44"/>
+      <c r="AA30" s="44"/>
     </row>
     <row r="31" spans="1:27" ht="15.75">
-      <c r="A31" s="157"/>
-      <c r="B31" s="47" t="s">
+      <c r="A31" s="146"/>
+      <c r="B31" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="48" t="s">
+      <c r="C31" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="45"/>
-      <c r="K31" s="45"/>
-      <c r="L31" s="45"/>
-      <c r="M31" s="45"/>
-      <c r="N31" s="45"/>
-      <c r="O31" s="45"/>
-      <c r="P31" s="45"/>
-      <c r="Q31" s="45"/>
-      <c r="R31" s="45"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="45"/>
-      <c r="U31" s="45"/>
-      <c r="V31" s="45"/>
-      <c r="W31" s="45"/>
-      <c r="X31" s="45"/>
-      <c r="Y31" s="45"/>
-      <c r="Z31" s="45"/>
-      <c r="AA31" s="45"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="44"/>
+      <c r="J31" s="44"/>
+      <c r="K31" s="44"/>
+      <c r="L31" s="44"/>
+      <c r="M31" s="44"/>
+      <c r="N31" s="44"/>
+      <c r="O31" s="44"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="44"/>
+      <c r="S31" s="44"/>
+      <c r="T31" s="44"/>
+      <c r="U31" s="44"/>
+      <c r="V31" s="44"/>
+      <c r="W31" s="44"/>
+      <c r="X31" s="44"/>
+      <c r="Y31" s="44"/>
+      <c r="Z31" s="44"/>
+      <c r="AA31" s="44"/>
     </row>
     <row r="32" spans="1:27" ht="15.75">
-      <c r="A32" s="157"/>
-      <c r="B32" s="47" t="s">
+      <c r="A32" s="146"/>
+      <c r="B32" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="48" t="s">
+      <c r="C32" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="45"/>
-      <c r="N32" s="45"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="45"/>
-      <c r="Q32" s="45"/>
-      <c r="R32" s="45"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="45"/>
-      <c r="U32" s="45"/>
-      <c r="V32" s="45"/>
-      <c r="W32" s="45"/>
-      <c r="X32" s="45"/>
-      <c r="Y32" s="45"/>
-      <c r="Z32" s="45"/>
-      <c r="AA32" s="45"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44"/>
+      <c r="L32" s="44"/>
+      <c r="M32" s="44"/>
+      <c r="N32" s="44"/>
+      <c r="O32" s="44"/>
+      <c r="P32" s="44"/>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="44"/>
+      <c r="S32" s="44"/>
+      <c r="T32" s="44"/>
+      <c r="U32" s="44"/>
+      <c r="V32" s="44"/>
+      <c r="W32" s="44"/>
+      <c r="X32" s="44"/>
+      <c r="Y32" s="44"/>
+      <c r="Z32" s="44"/>
+      <c r="AA32" s="44"/>
     </row>
     <row r="33" spans="1:27" ht="15.75">
-      <c r="A33" s="157"/>
-      <c r="B33" s="47" t="s">
+      <c r="A33" s="146"/>
+      <c r="B33" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="C33" s="48" t="s">
+      <c r="C33" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="45"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="45"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="45"/>
-      <c r="U33" s="45"/>
-      <c r="V33" s="45"/>
-      <c r="W33" s="45"/>
-      <c r="X33" s="45"/>
-      <c r="Y33" s="45"/>
-      <c r="Z33" s="45"/>
-      <c r="AA33" s="45"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="44"/>
+      <c r="L33" s="44"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="44"/>
+      <c r="O33" s="44"/>
+      <c r="P33" s="44"/>
+      <c r="Q33" s="44"/>
+      <c r="R33" s="44"/>
+      <c r="S33" s="44"/>
+      <c r="T33" s="44"/>
+      <c r="U33" s="44"/>
+      <c r="V33" s="44"/>
+      <c r="W33" s="44"/>
+      <c r="X33" s="44"/>
+      <c r="Y33" s="44"/>
+      <c r="Z33" s="44"/>
+      <c r="AA33" s="44"/>
     </row>
     <row r="34" spans="1:27" ht="15.75">
-      <c r="A34" s="156"/>
-      <c r="B34" s="47" t="s">
+      <c r="A34" s="145"/>
+      <c r="B34" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="C34" s="48" t="s">
+      <c r="C34" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="45"/>
-      <c r="M34" s="45"/>
-      <c r="N34" s="45"/>
-      <c r="O34" s="45"/>
-      <c r="P34" s="45"/>
-      <c r="Q34" s="45"/>
-      <c r="R34" s="45"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="45"/>
-      <c r="U34" s="45"/>
-      <c r="V34" s="45"/>
-      <c r="W34" s="45"/>
-      <c r="X34" s="45"/>
-      <c r="Y34" s="45"/>
-      <c r="Z34" s="45"/>
-      <c r="AA34" s="45"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="44"/>
+      <c r="K34" s="44"/>
+      <c r="L34" s="44"/>
+      <c r="M34" s="44"/>
+      <c r="N34" s="44"/>
+      <c r="O34" s="44"/>
+      <c r="P34" s="44"/>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="44"/>
+      <c r="S34" s="44"/>
+      <c r="T34" s="44"/>
+      <c r="U34" s="44"/>
+      <c r="V34" s="44"/>
+      <c r="W34" s="44"/>
+      <c r="X34" s="44"/>
+      <c r="Y34" s="44"/>
+      <c r="Z34" s="44"/>
+      <c r="AA34" s="44"/>
     </row>
     <row r="35" spans="1:27" ht="15.75">
-      <c r="A35" s="158" t="s">
+      <c r="A35" s="147" t="s">
         <v>138</v>
       </c>
-      <c r="B35" s="47" t="s">
+      <c r="B35" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="48" t="s">
+      <c r="C35" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
-      <c r="H35" s="45"/>
-      <c r="I35" s="45"/>
-      <c r="J35" s="45"/>
-      <c r="K35" s="45"/>
-      <c r="L35" s="45"/>
-      <c r="M35" s="45"/>
-      <c r="N35" s="45"/>
-      <c r="O35" s="45"/>
-      <c r="P35" s="45"/>
-      <c r="Q35" s="45"/>
-      <c r="R35" s="45"/>
-      <c r="S35" s="45"/>
-      <c r="T35" s="45"/>
-      <c r="U35" s="45"/>
-      <c r="V35" s="45"/>
-      <c r="W35" s="45"/>
-      <c r="X35" s="45"/>
-      <c r="Y35" s="45"/>
-      <c r="Z35" s="45"/>
-      <c r="AA35" s="45"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="44"/>
+      <c r="K35" s="44"/>
+      <c r="L35" s="44"/>
+      <c r="M35" s="44"/>
+      <c r="N35" s="44"/>
+      <c r="O35" s="44"/>
+      <c r="P35" s="44"/>
+      <c r="Q35" s="44"/>
+      <c r="R35" s="44"/>
+      <c r="S35" s="44"/>
+      <c r="T35" s="44"/>
+      <c r="U35" s="44"/>
+      <c r="V35" s="44"/>
+      <c r="W35" s="44"/>
+      <c r="X35" s="44"/>
+      <c r="Y35" s="44"/>
+      <c r="Z35" s="44"/>
+      <c r="AA35" s="44"/>
     </row>
     <row r="36" spans="1:27" ht="15.75">
-      <c r="A36" s="158"/>
-      <c r="B36" s="47" t="s">
+      <c r="A36" s="147"/>
+      <c r="B36" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="48" t="s">
+      <c r="C36" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="45"/>
-      <c r="K36" s="45"/>
-      <c r="L36" s="45"/>
-      <c r="M36" s="45"/>
-      <c r="N36" s="45"/>
-      <c r="O36" s="45"/>
-      <c r="P36" s="45"/>
-      <c r="Q36" s="45"/>
-      <c r="R36" s="45"/>
-      <c r="S36" s="45"/>
-      <c r="T36" s="45"/>
-      <c r="U36" s="45"/>
-      <c r="V36" s="45"/>
-      <c r="W36" s="45"/>
-      <c r="X36" s="45"/>
-      <c r="Y36" s="45"/>
-      <c r="Z36" s="45"/>
-      <c r="AA36" s="45"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="44"/>
+      <c r="K36" s="44"/>
+      <c r="L36" s="44"/>
+      <c r="M36" s="44"/>
+      <c r="N36" s="44"/>
+      <c r="O36" s="44"/>
+      <c r="P36" s="44"/>
+      <c r="Q36" s="44"/>
+      <c r="R36" s="44"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="44"/>
+      <c r="V36" s="44"/>
+      <c r="W36" s="44"/>
+      <c r="X36" s="44"/>
+      <c r="Y36" s="44"/>
+      <c r="Z36" s="44"/>
+      <c r="AA36" s="44"/>
     </row>
     <row r="37" spans="1:27" ht="15.75">
-      <c r="A37" s="158"/>
-      <c r="B37" s="47" t="s">
+      <c r="A37" s="147"/>
+      <c r="B37" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="48" t="s">
+      <c r="C37" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
-      <c r="H37" s="45"/>
-      <c r="I37" s="45"/>
-      <c r="J37" s="45"/>
-      <c r="K37" s="45"/>
-      <c r="L37" s="45"/>
-      <c r="M37" s="45"/>
-      <c r="N37" s="45"/>
-      <c r="O37" s="45"/>
-      <c r="P37" s="45"/>
-      <c r="Q37" s="45"/>
-      <c r="R37" s="45"/>
-      <c r="S37" s="45"/>
-      <c r="T37" s="45"/>
-      <c r="U37" s="45"/>
-      <c r="V37" s="45"/>
-      <c r="W37" s="45"/>
-      <c r="X37" s="45"/>
-      <c r="Y37" s="45"/>
-      <c r="Z37" s="45"/>
-      <c r="AA37" s="45"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="44"/>
+      <c r="L37" s="44"/>
+      <c r="M37" s="44"/>
+      <c r="N37" s="44"/>
+      <c r="O37" s="44"/>
+      <c r="P37" s="44"/>
+      <c r="Q37" s="44"/>
+      <c r="R37" s="44"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="44"/>
+      <c r="V37" s="44"/>
+      <c r="W37" s="44"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="44"/>
+      <c r="Z37" s="44"/>
+      <c r="AA37" s="44"/>
     </row>
     <row r="38" spans="1:27" ht="15.75">
-      <c r="A38" s="158"/>
-      <c r="B38" s="47" t="s">
+      <c r="A38" s="147"/>
+      <c r="B38" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="48" t="s">
+      <c r="C38" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="D38" s="45"/>
-      <c r="E38" s="45"/>
-      <c r="F38" s="45"/>
-      <c r="G38" s="45"/>
-      <c r="H38" s="45"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="45"/>
-      <c r="K38" s="45"/>
-      <c r="L38" s="45"/>
-      <c r="M38" s="45"/>
-      <c r="N38" s="45"/>
-      <c r="O38" s="45"/>
-      <c r="P38" s="45"/>
-      <c r="Q38" s="45"/>
-      <c r="R38" s="45"/>
-      <c r="S38" s="45"/>
-      <c r="T38" s="45"/>
-      <c r="U38" s="45"/>
-      <c r="V38" s="45"/>
-      <c r="W38" s="45"/>
-      <c r="X38" s="45"/>
-      <c r="Y38" s="45"/>
-      <c r="Z38" s="45"/>
-      <c r="AA38" s="45"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="44"/>
+      <c r="J38" s="44"/>
+      <c r="K38" s="44"/>
+      <c r="L38" s="44"/>
+      <c r="M38" s="44"/>
+      <c r="N38" s="44"/>
+      <c r="O38" s="44"/>
+      <c r="P38" s="44"/>
+      <c r="Q38" s="44"/>
+      <c r="R38" s="44"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="44"/>
+      <c r="V38" s="44"/>
+      <c r="W38" s="44"/>
+      <c r="X38" s="44"/>
+      <c r="Y38" s="44"/>
+      <c r="Z38" s="44"/>
+      <c r="AA38" s="44"/>
     </row>
     <row r="39" spans="1:27" ht="15.75">
-      <c r="A39" s="158"/>
-      <c r="B39" s="47" t="s">
+      <c r="A39" s="147"/>
+      <c r="B39" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="48" t="s">
+      <c r="C39" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="D39" s="45"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="45"/>
-      <c r="K39" s="45"/>
-      <c r="L39" s="45"/>
-      <c r="M39" s="45"/>
-      <c r="N39" s="45"/>
-      <c r="O39" s="45"/>
-      <c r="P39" s="45"/>
-      <c r="Q39" s="45"/>
-      <c r="R39" s="45"/>
-      <c r="S39" s="45"/>
-      <c r="T39" s="45"/>
-      <c r="U39" s="45"/>
-      <c r="V39" s="45"/>
-      <c r="W39" s="45"/>
-      <c r="X39" s="45"/>
-      <c r="Y39" s="45"/>
-      <c r="Z39" s="45"/>
-      <c r="AA39" s="45"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="44"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="44"/>
+      <c r="J39" s="44"/>
+      <c r="K39" s="44"/>
+      <c r="L39" s="44"/>
+      <c r="M39" s="44"/>
+      <c r="N39" s="44"/>
+      <c r="O39" s="44"/>
+      <c r="P39" s="44"/>
+      <c r="Q39" s="44"/>
+      <c r="R39" s="44"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="44"/>
+      <c r="V39" s="44"/>
+      <c r="W39" s="44"/>
+      <c r="X39" s="44"/>
+      <c r="Y39" s="44"/>
+      <c r="Z39" s="44"/>
+      <c r="AA39" s="44"/>
     </row>
     <row r="40" spans="1:27" ht="15.75">
-      <c r="A40" s="158"/>
-      <c r="B40" s="47" t="s">
+      <c r="A40" s="147"/>
+      <c r="B40" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C40" s="48" t="s">
+      <c r="C40" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="45"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="45"/>
-      <c r="K40" s="45"/>
-      <c r="L40" s="45"/>
-      <c r="M40" s="45"/>
-      <c r="N40" s="45"/>
-      <c r="O40" s="45"/>
-      <c r="P40" s="45"/>
-      <c r="Q40" s="45"/>
-      <c r="R40" s="45"/>
-      <c r="S40" s="45"/>
-      <c r="T40" s="45"/>
-      <c r="U40" s="45"/>
-      <c r="V40" s="45"/>
-      <c r="W40" s="45"/>
-      <c r="X40" s="45"/>
-      <c r="Y40" s="45"/>
-      <c r="Z40" s="45"/>
-      <c r="AA40" s="45"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="44"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="44"/>
+      <c r="J40" s="44"/>
+      <c r="K40" s="44"/>
+      <c r="L40" s="44"/>
+      <c r="M40" s="44"/>
+      <c r="N40" s="44"/>
+      <c r="O40" s="44"/>
+      <c r="P40" s="44"/>
+      <c r="Q40" s="44"/>
+      <c r="R40" s="44"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="44"/>
+      <c r="V40" s="44"/>
+      <c r="W40" s="44"/>
+      <c r="X40" s="44"/>
+      <c r="Y40" s="44"/>
+      <c r="Z40" s="44"/>
+      <c r="AA40" s="44"/>
     </row>
     <row r="41" spans="1:27" ht="15.75">
-      <c r="A41" s="158"/>
-      <c r="B41" s="47" t="s">
+      <c r="A41" s="147"/>
+      <c r="B41" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="C41" s="48" t="s">
+      <c r="C41" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="D41" s="45"/>
-      <c r="E41" s="45"/>
-      <c r="F41" s="45"/>
-      <c r="G41" s="45"/>
-      <c r="H41" s="45"/>
-      <c r="I41" s="45"/>
-      <c r="J41" s="45"/>
-      <c r="K41" s="45"/>
-      <c r="L41" s="45"/>
-      <c r="M41" s="45"/>
-      <c r="N41" s="45"/>
-      <c r="O41" s="45"/>
-      <c r="P41" s="45"/>
-      <c r="Q41" s="45"/>
-      <c r="R41" s="45"/>
-      <c r="S41" s="45"/>
-      <c r="T41" s="45"/>
-      <c r="U41" s="45"/>
-      <c r="V41" s="45"/>
-      <c r="W41" s="45"/>
-      <c r="X41" s="45"/>
-      <c r="Y41" s="45"/>
-      <c r="Z41" s="45"/>
-      <c r="AA41" s="45"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="44"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="44"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="44"/>
+      <c r="J41" s="44"/>
+      <c r="K41" s="44"/>
+      <c r="L41" s="44"/>
+      <c r="M41" s="44"/>
+      <c r="N41" s="44"/>
+      <c r="O41" s="44"/>
+      <c r="P41" s="44"/>
+      <c r="Q41" s="44"/>
+      <c r="R41" s="44"/>
+      <c r="S41" s="44"/>
+      <c r="T41" s="44"/>
+      <c r="U41" s="44"/>
+      <c r="V41" s="44"/>
+      <c r="W41" s="44"/>
+      <c r="X41" s="44"/>
+      <c r="Y41" s="44"/>
+      <c r="Z41" s="44"/>
+      <c r="AA41" s="44"/>
     </row>
     <row r="42" spans="1:27" ht="15.75">
-      <c r="A42" s="158"/>
-      <c r="B42" s="47" t="s">
+      <c r="A42" s="147"/>
+      <c r="B42" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="C42" s="48" t="s">
+      <c r="C42" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="D42" s="45"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="45"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="45"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="45"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="45"/>
-      <c r="M42" s="45"/>
-      <c r="N42" s="45"/>
-      <c r="O42" s="45"/>
-      <c r="P42" s="45"/>
-      <c r="Q42" s="45"/>
-      <c r="R42" s="45"/>
-      <c r="S42" s="45"/>
-      <c r="T42" s="45"/>
-      <c r="U42" s="45"/>
-      <c r="V42" s="45"/>
-      <c r="W42" s="45"/>
-      <c r="X42" s="45"/>
-      <c r="Y42" s="45"/>
-      <c r="Z42" s="45"/>
-      <c r="AA42" s="45"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="44"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="44"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="44"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="44"/>
+      <c r="L42" s="44"/>
+      <c r="M42" s="44"/>
+      <c r="N42" s="44"/>
+      <c r="O42" s="44"/>
+      <c r="P42" s="44"/>
+      <c r="Q42" s="44"/>
+      <c r="R42" s="44"/>
+      <c r="S42" s="44"/>
+      <c r="T42" s="44"/>
+      <c r="U42" s="44"/>
+      <c r="V42" s="44"/>
+      <c r="W42" s="44"/>
+      <c r="X42" s="44"/>
+      <c r="Y42" s="44"/>
+      <c r="Z42" s="44"/>
+      <c r="AA42" s="44"/>
     </row>
     <row r="43" spans="1:27" ht="15.75">
-      <c r="A43" s="158"/>
-      <c r="B43" s="47" t="s">
+      <c r="A43" s="147"/>
+      <c r="B43" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="C43" s="48" t="s">
+      <c r="C43" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="D43" s="45"/>
-      <c r="E43" s="45"/>
-      <c r="F43" s="45"/>
-      <c r="G43" s="45"/>
-      <c r="H43" s="45"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="45"/>
-      <c r="K43" s="45"/>
-      <c r="L43" s="45"/>
-      <c r="M43" s="45"/>
-      <c r="N43" s="45"/>
-      <c r="O43" s="45"/>
-      <c r="P43" s="45"/>
-      <c r="Q43" s="45"/>
-      <c r="R43" s="45"/>
-      <c r="S43" s="45"/>
-      <c r="T43" s="45"/>
-      <c r="U43" s="45"/>
-      <c r="V43" s="45"/>
-      <c r="W43" s="45"/>
-      <c r="X43" s="45"/>
-      <c r="Y43" s="45"/>
-      <c r="Z43" s="45"/>
-      <c r="AA43" s="45"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="44"/>
+      <c r="V43" s="44"/>
+      <c r="W43" s="44"/>
+      <c r="X43" s="44"/>
+      <c r="Y43" s="44"/>
+      <c r="Z43" s="44"/>
+      <c r="AA43" s="44"/>
     </row>
     <row r="44" spans="1:27" ht="15.75">
-      <c r="A44" s="158"/>
-      <c r="B44" s="47" t="s">
+      <c r="A44" s="147"/>
+      <c r="B44" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="C44" s="48" t="s">
+      <c r="C44" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="D44" s="45"/>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
-      <c r="G44" s="45"/>
-      <c r="H44" s="45"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="45"/>
-      <c r="K44" s="45"/>
-      <c r="L44" s="45"/>
-      <c r="M44" s="45"/>
-      <c r="N44" s="45"/>
-      <c r="O44" s="45"/>
-      <c r="P44" s="45"/>
-      <c r="Q44" s="45"/>
-      <c r="R44" s="45"/>
-      <c r="S44" s="45"/>
-      <c r="T44" s="45"/>
-      <c r="U44" s="45"/>
-      <c r="V44" s="45"/>
-      <c r="W44" s="45"/>
-      <c r="X44" s="45"/>
-      <c r="Y44" s="45"/>
-      <c r="Z44" s="45"/>
-      <c r="AA44" s="45"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="44"/>
+      <c r="K44" s="44"/>
+      <c r="L44" s="44"/>
+      <c r="M44" s="44"/>
+      <c r="N44" s="44"/>
+      <c r="O44" s="44"/>
+      <c r="P44" s="44"/>
+      <c r="Q44" s="44"/>
+      <c r="R44" s="44"/>
+      <c r="S44" s="44"/>
+      <c r="T44" s="44"/>
+      <c r="U44" s="44"/>
+      <c r="V44" s="44"/>
+      <c r="W44" s="44"/>
+      <c r="X44" s="44"/>
+      <c r="Y44" s="44"/>
+      <c r="Z44" s="44"/>
+      <c r="AA44" s="44"/>
     </row>
     <row r="45" spans="1:27" ht="15.75">
-      <c r="A45" s="158"/>
-      <c r="B45" s="47" t="s">
+      <c r="A45" s="147"/>
+      <c r="B45" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="C45" s="48" t="s">
+      <c r="C45" s="47" t="s">
         <v>108</v>
       </c>
-      <c r="D45" s="45"/>
-      <c r="E45" s="45"/>
-      <c r="F45" s="45"/>
-      <c r="G45" s="45"/>
-      <c r="H45" s="45"/>
-      <c r="I45" s="45"/>
-      <c r="J45" s="45"/>
-      <c r="K45" s="45"/>
-      <c r="L45" s="45"/>
-      <c r="M45" s="45"/>
-      <c r="N45" s="45"/>
-      <c r="O45" s="45"/>
-      <c r="P45" s="45"/>
-      <c r="Q45" s="45"/>
-      <c r="R45" s="45"/>
-      <c r="S45" s="45"/>
-      <c r="T45" s="45"/>
-      <c r="U45" s="45"/>
-      <c r="V45" s="45"/>
-      <c r="W45" s="45"/>
-      <c r="X45" s="45"/>
-      <c r="Y45" s="45"/>
-      <c r="Z45" s="45"/>
-      <c r="AA45" s="45"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="44"/>
+      <c r="J45" s="44"/>
+      <c r="K45" s="44"/>
+      <c r="L45" s="44"/>
+      <c r="M45" s="44"/>
+      <c r="N45" s="44"/>
+      <c r="O45" s="44"/>
+      <c r="P45" s="44"/>
+      <c r="Q45" s="44"/>
+      <c r="R45" s="44"/>
+      <c r="S45" s="44"/>
+      <c r="T45" s="44"/>
+      <c r="U45" s="44"/>
+      <c r="V45" s="44"/>
+      <c r="W45" s="44"/>
+      <c r="X45" s="44"/>
+      <c r="Y45" s="44"/>
+      <c r="Z45" s="44"/>
+      <c r="AA45" s="44"/>
     </row>
     <row r="46" spans="1:27" ht="15.75">
-      <c r="A46" s="158"/>
-      <c r="B46" s="47" t="s">
+      <c r="A46" s="147"/>
+      <c r="B46" s="46" t="s">
         <v>136</v>
       </c>
-      <c r="C46" s="48" t="s">
+      <c r="C46" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="D46" s="45"/>
-      <c r="E46" s="45"/>
-      <c r="F46" s="45"/>
-      <c r="G46" s="45"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45"/>
-      <c r="J46" s="45"/>
-      <c r="K46" s="45"/>
-      <c r="L46" s="45"/>
-      <c r="M46" s="45"/>
-      <c r="N46" s="45"/>
-      <c r="O46" s="45"/>
-      <c r="P46" s="45"/>
-      <c r="Q46" s="45"/>
-      <c r="R46" s="45"/>
-      <c r="S46" s="45"/>
-      <c r="T46" s="45"/>
-      <c r="U46" s="45"/>
-      <c r="V46" s="45"/>
-      <c r="W46" s="45"/>
-      <c r="X46" s="45"/>
-      <c r="Y46" s="45"/>
-      <c r="Z46" s="45"/>
-      <c r="AA46" s="45"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="44"/>
+      <c r="K46" s="44"/>
+      <c r="L46" s="44"/>
+      <c r="M46" s="44"/>
+      <c r="N46" s="44"/>
+      <c r="O46" s="44"/>
+      <c r="P46" s="44"/>
+      <c r="Q46" s="44"/>
+      <c r="R46" s="44"/>
+      <c r="S46" s="44"/>
+      <c r="T46" s="44"/>
+      <c r="U46" s="44"/>
+      <c r="V46" s="44"/>
+      <c r="W46" s="44"/>
+      <c r="X46" s="44"/>
+      <c r="Y46" s="44"/>
+      <c r="Z46" s="44"/>
+      <c r="AA46" s="44"/>
     </row>
     <row r="47" spans="1:27" ht="15.75">
-      <c r="A47" s="158"/>
-      <c r="B47" s="47" t="s">
+      <c r="A47" s="147"/>
+      <c r="B47" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="C47" s="48" t="s">
+      <c r="C47" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="D47" s="45"/>
-      <c r="E47" s="45"/>
-      <c r="F47" s="45"/>
-      <c r="G47" s="45"/>
-      <c r="H47" s="45"/>
-      <c r="I47" s="45"/>
-      <c r="J47" s="45"/>
-      <c r="K47" s="45"/>
-      <c r="L47" s="45"/>
-      <c r="M47" s="45"/>
-      <c r="N47" s="45"/>
-      <c r="O47" s="45"/>
-      <c r="P47" s="45"/>
-      <c r="Q47" s="45"/>
-      <c r="R47" s="45"/>
-      <c r="S47" s="45"/>
-      <c r="T47" s="45"/>
-      <c r="U47" s="45"/>
-      <c r="V47" s="45"/>
-      <c r="W47" s="45"/>
-      <c r="X47" s="45"/>
-      <c r="Y47" s="45"/>
-      <c r="Z47" s="45"/>
-      <c r="AA47" s="45"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="44"/>
+      <c r="F47" s="44"/>
+      <c r="G47" s="44"/>
+      <c r="H47" s="44"/>
+      <c r="I47" s="44"/>
+      <c r="J47" s="44"/>
+      <c r="K47" s="44"/>
+      <c r="L47" s="44"/>
+      <c r="M47" s="44"/>
+      <c r="N47" s="44"/>
+      <c r="O47" s="44"/>
+      <c r="P47" s="44"/>
+      <c r="Q47" s="44"/>
+      <c r="R47" s="44"/>
+      <c r="S47" s="44"/>
+      <c r="T47" s="44"/>
+      <c r="U47" s="44"/>
+      <c r="V47" s="44"/>
+      <c r="W47" s="44"/>
+      <c r="X47" s="44"/>
+      <c r="Y47" s="44"/>
+      <c r="Z47" s="44"/>
+      <c r="AA47" s="44"/>
     </row>
     <row r="48" spans="1:27" ht="15.75">
-      <c r="A48" s="158"/>
-      <c r="B48" s="47" t="s">
+      <c r="A48" s="147"/>
+      <c r="B48" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="48" t="s">
+      <c r="C48" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="D48" s="45"/>
-      <c r="E48" s="45"/>
-      <c r="F48" s="45"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="45"/>
-      <c r="K48" s="45"/>
-      <c r="L48" s="45"/>
-      <c r="M48" s="45"/>
-      <c r="N48" s="45"/>
-      <c r="O48" s="45"/>
-      <c r="P48" s="45"/>
-      <c r="Q48" s="45"/>
-      <c r="R48" s="45"/>
-      <c r="S48" s="45"/>
-      <c r="T48" s="45"/>
-      <c r="U48" s="45"/>
-      <c r="V48" s="45"/>
-      <c r="W48" s="45"/>
-      <c r="X48" s="45"/>
-      <c r="Y48" s="45"/>
-      <c r="Z48" s="45"/>
-      <c r="AA48" s="45"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="44"/>
+      <c r="F48" s="44"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="44"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="44"/>
+      <c r="K48" s="44"/>
+      <c r="L48" s="44"/>
+      <c r="M48" s="44"/>
+      <c r="N48" s="44"/>
+      <c r="O48" s="44"/>
+      <c r="P48" s="44"/>
+      <c r="Q48" s="44"/>
+      <c r="R48" s="44"/>
+      <c r="S48" s="44"/>
+      <c r="T48" s="44"/>
+      <c r="U48" s="44"/>
+      <c r="V48" s="44"/>
+      <c r="W48" s="44"/>
+      <c r="X48" s="44"/>
+      <c r="Y48" s="44"/>
+      <c r="Z48" s="44"/>
+      <c r="AA48" s="44"/>
     </row>
     <row r="49" spans="1:27" ht="15.75">
-      <c r="A49" s="158"/>
-      <c r="B49" s="47" t="s">
+      <c r="A49" s="147"/>
+      <c r="B49" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="48" t="s">
+      <c r="C49" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="45"/>
-      <c r="E49" s="45"/>
-      <c r="F49" s="45"/>
-      <c r="G49" s="45"/>
-      <c r="H49" s="45"/>
-      <c r="I49" s="45"/>
-      <c r="J49" s="45"/>
-      <c r="K49" s="45"/>
-      <c r="L49" s="45"/>
-      <c r="M49" s="45"/>
-      <c r="N49" s="45"/>
-      <c r="O49" s="45"/>
-      <c r="P49" s="45"/>
-      <c r="Q49" s="45"/>
-      <c r="R49" s="45"/>
-      <c r="S49" s="45"/>
-      <c r="T49" s="45"/>
-      <c r="U49" s="45"/>
-      <c r="V49" s="45"/>
-      <c r="W49" s="45"/>
-      <c r="X49" s="45"/>
-      <c r="Y49" s="45"/>
-      <c r="Z49" s="45"/>
-      <c r="AA49" s="45"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="44"/>
+      <c r="F49" s="44"/>
+      <c r="G49" s="44"/>
+      <c r="H49" s="44"/>
+      <c r="I49" s="44"/>
+      <c r="J49" s="44"/>
+      <c r="K49" s="44"/>
+      <c r="L49" s="44"/>
+      <c r="M49" s="44"/>
+      <c r="N49" s="44"/>
+      <c r="O49" s="44"/>
+      <c r="P49" s="44"/>
+      <c r="Q49" s="44"/>
+      <c r="R49" s="44"/>
+      <c r="S49" s="44"/>
+      <c r="T49" s="44"/>
+      <c r="U49" s="44"/>
+      <c r="V49" s="44"/>
+      <c r="W49" s="44"/>
+      <c r="X49" s="44"/>
+      <c r="Y49" s="44"/>
+      <c r="Z49" s="44"/>
+      <c r="AA49" s="44"/>
     </row>
     <row r="50" spans="1:27" ht="15.75">
-      <c r="A50" s="158"/>
-      <c r="B50" s="47" t="s">
+      <c r="A50" s="147"/>
+      <c r="B50" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="C50" s="48" t="s">
+      <c r="C50" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="D50" s="45"/>
-      <c r="E50" s="45"/>
-      <c r="F50" s="45"/>
-      <c r="G50" s="45"/>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="45"/>
-      <c r="K50" s="45"/>
-      <c r="L50" s="45"/>
-      <c r="M50" s="45"/>
-      <c r="N50" s="45"/>
-      <c r="O50" s="45"/>
-      <c r="P50" s="45"/>
-      <c r="Q50" s="45"/>
-      <c r="R50" s="45"/>
-      <c r="S50" s="45"/>
-      <c r="T50" s="45"/>
-      <c r="U50" s="45"/>
-      <c r="V50" s="45"/>
-      <c r="W50" s="45"/>
-      <c r="X50" s="45"/>
-      <c r="Y50" s="45"/>
-      <c r="Z50" s="45"/>
-      <c r="AA50" s="45"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="44"/>
+      <c r="L50" s="44"/>
+      <c r="M50" s="44"/>
+      <c r="N50" s="44"/>
+      <c r="O50" s="44"/>
+      <c r="P50" s="44"/>
+      <c r="Q50" s="44"/>
+      <c r="R50" s="44"/>
+      <c r="S50" s="44"/>
+      <c r="T50" s="44"/>
+      <c r="U50" s="44"/>
+      <c r="V50" s="44"/>
+      <c r="W50" s="44"/>
+      <c r="X50" s="44"/>
+      <c r="Y50" s="44"/>
+      <c r="Z50" s="44"/>
+      <c r="AA50" s="44"/>
     </row>
     <row r="51" spans="1:27" ht="15.75">
-      <c r="A51" s="158"/>
-      <c r="B51" s="47" t="s">
+      <c r="A51" s="147"/>
+      <c r="B51" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="C51" s="48" t="s">
+      <c r="C51" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="D51" s="45"/>
-      <c r="E51" s="45"/>
-      <c r="F51" s="45"/>
-      <c r="G51" s="45"/>
-      <c r="H51" s="45"/>
-      <c r="I51" s="45"/>
-      <c r="J51" s="45"/>
-      <c r="K51" s="45"/>
-      <c r="L51" s="45"/>
-      <c r="M51" s="45"/>
-      <c r="N51" s="45"/>
-      <c r="O51" s="45"/>
-      <c r="P51" s="45"/>
-      <c r="Q51" s="45"/>
-      <c r="R51" s="45"/>
-      <c r="S51" s="45"/>
-      <c r="T51" s="45"/>
-      <c r="U51" s="45"/>
-      <c r="V51" s="45"/>
-      <c r="W51" s="45"/>
-      <c r="X51" s="45"/>
-      <c r="Y51" s="45"/>
-      <c r="Z51" s="45"/>
-      <c r="AA51" s="45"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="44"/>
+      <c r="F51" s="44"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="44"/>
+      <c r="I51" s="44"/>
+      <c r="J51" s="44"/>
+      <c r="K51" s="44"/>
+      <c r="L51" s="44"/>
+      <c r="M51" s="44"/>
+      <c r="N51" s="44"/>
+      <c r="O51" s="44"/>
+      <c r="P51" s="44"/>
+      <c r="Q51" s="44"/>
+      <c r="R51" s="44"/>
+      <c r="S51" s="44"/>
+      <c r="T51" s="44"/>
+      <c r="U51" s="44"/>
+      <c r="V51" s="44"/>
+      <c r="W51" s="44"/>
+      <c r="X51" s="44"/>
+      <c r="Y51" s="44"/>
+      <c r="Z51" s="44"/>
+      <c r="AA51" s="44"/>
     </row>
     <row r="52" spans="1:27" ht="15.75">
-      <c r="A52" s="158"/>
-      <c r="B52" s="47" t="s">
+      <c r="A52" s="147"/>
+      <c r="B52" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="C52" s="48" t="s">
+      <c r="C52" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="D52" s="45"/>
-      <c r="E52" s="45"/>
-      <c r="F52" s="45"/>
-      <c r="G52" s="45"/>
-      <c r="H52" s="45"/>
-      <c r="I52" s="45"/>
-      <c r="J52" s="45"/>
-      <c r="K52" s="45"/>
-      <c r="L52" s="45"/>
-      <c r="M52" s="45"/>
-      <c r="N52" s="45"/>
-      <c r="O52" s="45"/>
-      <c r="P52" s="45"/>
-      <c r="Q52" s="45"/>
-      <c r="R52" s="45"/>
-      <c r="S52" s="45"/>
-      <c r="T52" s="45"/>
-      <c r="U52" s="45"/>
-      <c r="V52" s="45"/>
-      <c r="W52" s="45"/>
-      <c r="X52" s="45"/>
-      <c r="Y52" s="45"/>
-      <c r="Z52" s="45"/>
-      <c r="AA52" s="45"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="44"/>
+      <c r="G52" s="44"/>
+      <c r="H52" s="44"/>
+      <c r="I52" s="44"/>
+      <c r="J52" s="44"/>
+      <c r="K52" s="44"/>
+      <c r="L52" s="44"/>
+      <c r="M52" s="44"/>
+      <c r="N52" s="44"/>
+      <c r="O52" s="44"/>
+      <c r="P52" s="44"/>
+      <c r="Q52" s="44"/>
+      <c r="R52" s="44"/>
+      <c r="S52" s="44"/>
+      <c r="T52" s="44"/>
+      <c r="U52" s="44"/>
+      <c r="V52" s="44"/>
+      <c r="W52" s="44"/>
+      <c r="X52" s="44"/>
+      <c r="Y52" s="44"/>
+      <c r="Z52" s="44"/>
+      <c r="AA52" s="44"/>
     </row>
     <row r="53" spans="1:27" ht="15.75">
-      <c r="A53" s="158"/>
-      <c r="B53" s="47" t="s">
+      <c r="A53" s="147"/>
+      <c r="B53" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C53" s="48" t="s">
+      <c r="C53" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="D53" s="45"/>
-      <c r="E53" s="45"/>
-      <c r="F53" s="45"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="45"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="45"/>
-      <c r="K53" s="45"/>
-      <c r="L53" s="45"/>
-      <c r="M53" s="45"/>
-      <c r="N53" s="45"/>
-      <c r="O53" s="45"/>
-      <c r="P53" s="45"/>
-      <c r="Q53" s="45"/>
-      <c r="R53" s="45"/>
-      <c r="S53" s="45"/>
-      <c r="T53" s="45"/>
-      <c r="U53" s="45"/>
-      <c r="V53" s="45"/>
-      <c r="W53" s="45"/>
-      <c r="X53" s="45"/>
-      <c r="Y53" s="45"/>
-      <c r="Z53" s="45"/>
-      <c r="AA53" s="45"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="44"/>
+      <c r="J53" s="44"/>
+      <c r="K53" s="44"/>
+      <c r="L53" s="44"/>
+      <c r="M53" s="44"/>
+      <c r="N53" s="44"/>
+      <c r="O53" s="44"/>
+      <c r="P53" s="44"/>
+      <c r="Q53" s="44"/>
+      <c r="R53" s="44"/>
+      <c r="S53" s="44"/>
+      <c r="T53" s="44"/>
+      <c r="U53" s="44"/>
+      <c r="V53" s="44"/>
+      <c r="W53" s="44"/>
+      <c r="X53" s="44"/>
+      <c r="Y53" s="44"/>
+      <c r="Z53" s="44"/>
+      <c r="AA53" s="44"/>
     </row>
     <row r="54" spans="1:27" ht="15.75">
-      <c r="A54" s="158"/>
-      <c r="B54" s="47" t="s">
+      <c r="A54" s="147"/>
+      <c r="B54" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C54" s="48" t="s">
+      <c r="C54" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="D54" s="45"/>
-      <c r="E54" s="45"/>
-      <c r="F54" s="45"/>
-      <c r="G54" s="45"/>
-      <c r="H54" s="45"/>
-      <c r="I54" s="45"/>
-      <c r="J54" s="45"/>
-      <c r="K54" s="45"/>
-      <c r="L54" s="45"/>
-      <c r="M54" s="45"/>
-      <c r="N54" s="45"/>
-      <c r="O54" s="45"/>
-      <c r="P54" s="45"/>
-      <c r="Q54" s="45"/>
-      <c r="R54" s="45"/>
-      <c r="S54" s="45"/>
-      <c r="T54" s="45"/>
-      <c r="U54" s="45"/>
-      <c r="V54" s="45"/>
-      <c r="W54" s="45"/>
-      <c r="X54" s="45"/>
-      <c r="Y54" s="45"/>
-      <c r="Z54" s="45"/>
-      <c r="AA54" s="45"/>
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="44"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="44"/>
+      <c r="J54" s="44"/>
+      <c r="K54" s="44"/>
+      <c r="L54" s="44"/>
+      <c r="M54" s="44"/>
+      <c r="N54" s="44"/>
+      <c r="O54" s="44"/>
+      <c r="P54" s="44"/>
+      <c r="Q54" s="44"/>
+      <c r="R54" s="44"/>
+      <c r="S54" s="44"/>
+      <c r="T54" s="44"/>
+      <c r="U54" s="44"/>
+      <c r="V54" s="44"/>
+      <c r="W54" s="44"/>
+      <c r="X54" s="44"/>
+      <c r="Y54" s="44"/>
+      <c r="Z54" s="44"/>
+      <c r="AA54" s="44"/>
     </row>
     <row r="55" spans="1:27" ht="15.75">
-      <c r="A55" s="158"/>
-      <c r="B55" s="47" t="s">
+      <c r="A55" s="147"/>
+      <c r="B55" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C55" s="48" t="s">
+      <c r="C55" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="D55" s="45"/>
-      <c r="E55" s="45"/>
-      <c r="F55" s="45"/>
-      <c r="G55" s="45"/>
-      <c r="H55" s="45"/>
-      <c r="I55" s="45"/>
-      <c r="J55" s="45"/>
-      <c r="K55" s="45"/>
-      <c r="L55" s="45"/>
-      <c r="M55" s="45"/>
-      <c r="N55" s="45"/>
-      <c r="O55" s="45"/>
-      <c r="P55" s="45"/>
-      <c r="Q55" s="45"/>
-      <c r="R55" s="45"/>
-      <c r="S55" s="45"/>
-      <c r="T55" s="45"/>
-      <c r="U55" s="45"/>
-      <c r="V55" s="45"/>
-      <c r="W55" s="45"/>
-      <c r="X55" s="45"/>
-      <c r="Y55" s="45"/>
-      <c r="Z55" s="45"/>
-      <c r="AA55" s="45"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="44"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="44"/>
+      <c r="I55" s="44"/>
+      <c r="J55" s="44"/>
+      <c r="K55" s="44"/>
+      <c r="L55" s="44"/>
+      <c r="M55" s="44"/>
+      <c r="N55" s="44"/>
+      <c r="O55" s="44"/>
+      <c r="P55" s="44"/>
+      <c r="Q55" s="44"/>
+      <c r="R55" s="44"/>
+      <c r="S55" s="44"/>
+      <c r="T55" s="44"/>
+      <c r="U55" s="44"/>
+      <c r="V55" s="44"/>
+      <c r="W55" s="44"/>
+      <c r="X55" s="44"/>
+      <c r="Y55" s="44"/>
+      <c r="Z55" s="44"/>
+      <c r="AA55" s="44"/>
     </row>
     <row r="56" spans="1:27" ht="15.75">
-      <c r="A56" s="158"/>
-      <c r="B56" s="47" t="s">
+      <c r="A56" s="147"/>
+      <c r="B56" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C56" s="48" t="s">
+      <c r="C56" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="D56" s="45"/>
-      <c r="E56" s="45"/>
-      <c r="F56" s="45"/>
-      <c r="G56" s="45"/>
-      <c r="H56" s="45"/>
-      <c r="I56" s="45"/>
-      <c r="J56" s="45"/>
-      <c r="K56" s="45"/>
-      <c r="L56" s="45"/>
-      <c r="M56" s="45"/>
-      <c r="N56" s="45"/>
-      <c r="O56" s="45"/>
-      <c r="P56" s="45"/>
-      <c r="Q56" s="45"/>
-      <c r="R56" s="45"/>
-      <c r="S56" s="45"/>
-      <c r="T56" s="45"/>
-      <c r="U56" s="45"/>
-      <c r="V56" s="45"/>
-      <c r="W56" s="45"/>
-      <c r="X56" s="45"/>
-      <c r="Y56" s="45"/>
-      <c r="Z56" s="45"/>
-      <c r="AA56" s="45"/>
+      <c r="D56" s="44"/>
+      <c r="E56" s="44"/>
+      <c r="F56" s="44"/>
+      <c r="G56" s="44"/>
+      <c r="H56" s="44"/>
+      <c r="I56" s="44"/>
+      <c r="J56" s="44"/>
+      <c r="K56" s="44"/>
+      <c r="L56" s="44"/>
+      <c r="M56" s="44"/>
+      <c r="N56" s="44"/>
+      <c r="O56" s="44"/>
+      <c r="P56" s="44"/>
+      <c r="Q56" s="44"/>
+      <c r="R56" s="44"/>
+      <c r="S56" s="44"/>
+      <c r="T56" s="44"/>
+      <c r="U56" s="44"/>
+      <c r="V56" s="44"/>
+      <c r="W56" s="44"/>
+      <c r="X56" s="44"/>
+      <c r="Y56" s="44"/>
+      <c r="Z56" s="44"/>
+      <c r="AA56" s="44"/>
     </row>
     <row r="57" spans="1:27" ht="15.75">
-      <c r="A57" s="158"/>
-      <c r="B57" s="47" t="s">
+      <c r="A57" s="147"/>
+      <c r="B57" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="C57" s="48" t="s">
+      <c r="C57" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="D57" s="45"/>
-      <c r="E57" s="45"/>
-      <c r="F57" s="45"/>
-      <c r="G57" s="45"/>
-      <c r="H57" s="45"/>
-      <c r="I57" s="45"/>
-      <c r="J57" s="45"/>
-      <c r="K57" s="45"/>
-      <c r="L57" s="45"/>
-      <c r="M57" s="45"/>
-      <c r="N57" s="45"/>
-      <c r="O57" s="45"/>
-      <c r="P57" s="45"/>
-      <c r="Q57" s="45"/>
-      <c r="R57" s="45"/>
-      <c r="S57" s="45"/>
-      <c r="T57" s="45"/>
-      <c r="U57" s="45"/>
-      <c r="V57" s="45"/>
-      <c r="W57" s="45"/>
-      <c r="X57" s="45"/>
-      <c r="Y57" s="45"/>
-      <c r="Z57" s="45"/>
-      <c r="AA57" s="45"/>
+      <c r="D57" s="44"/>
+      <c r="E57" s="44"/>
+      <c r="F57" s="44"/>
+      <c r="G57" s="44"/>
+      <c r="H57" s="44"/>
+      <c r="I57" s="44"/>
+      <c r="J57" s="44"/>
+      <c r="K57" s="44"/>
+      <c r="L57" s="44"/>
+      <c r="M57" s="44"/>
+      <c r="N57" s="44"/>
+      <c r="O57" s="44"/>
+      <c r="P57" s="44"/>
+      <c r="Q57" s="44"/>
+      <c r="R57" s="44"/>
+      <c r="S57" s="44"/>
+      <c r="T57" s="44"/>
+      <c r="U57" s="44"/>
+      <c r="V57" s="44"/>
+      <c r="W57" s="44"/>
+      <c r="X57" s="44"/>
+      <c r="Y57" s="44"/>
+      <c r="Z57" s="44"/>
+      <c r="AA57" s="44"/>
     </row>
     <row r="58" spans="1:27" ht="15.75">
-      <c r="A58" s="158"/>
-      <c r="B58" s="47" t="s">
+      <c r="A58" s="147"/>
+      <c r="B58" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="C58" s="48" t="s">
+      <c r="C58" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="D58" s="45"/>
-      <c r="E58" s="45"/>
-      <c r="F58" s="45"/>
-      <c r="G58" s="45"/>
-      <c r="H58" s="45"/>
-      <c r="I58" s="45"/>
-      <c r="J58" s="45"/>
-      <c r="K58" s="45"/>
-      <c r="L58" s="45"/>
-      <c r="M58" s="45"/>
-      <c r="N58" s="45"/>
-      <c r="O58" s="45"/>
-      <c r="P58" s="45"/>
-      <c r="Q58" s="45"/>
-      <c r="R58" s="45"/>
-      <c r="S58" s="45"/>
-      <c r="T58" s="45"/>
-      <c r="U58" s="45"/>
-      <c r="V58" s="45"/>
-      <c r="W58" s="45"/>
-      <c r="X58" s="45"/>
-      <c r="Y58" s="45"/>
-      <c r="Z58" s="45"/>
-      <c r="AA58" s="45"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
+      <c r="F58" s="44"/>
+      <c r="G58" s="44"/>
+      <c r="H58" s="44"/>
+      <c r="I58" s="44"/>
+      <c r="J58" s="44"/>
+      <c r="K58" s="44"/>
+      <c r="L58" s="44"/>
+      <c r="M58" s="44"/>
+      <c r="N58" s="44"/>
+      <c r="O58" s="44"/>
+      <c r="P58" s="44"/>
+      <c r="Q58" s="44"/>
+      <c r="R58" s="44"/>
+      <c r="S58" s="44"/>
+      <c r="T58" s="44"/>
+      <c r="U58" s="44"/>
+      <c r="V58" s="44"/>
+      <c r="W58" s="44"/>
+      <c r="X58" s="44"/>
+      <c r="Y58" s="44"/>
+      <c r="Z58" s="44"/>
+      <c r="AA58" s="44"/>
+    </row>
+    <row r="59" spans="1:27" ht="15.75">
+      <c r="A59" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="B59" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" s="155" t="s">
+        <v>142</v>
+      </c>
+      <c r="D59" s="156"/>
+      <c r="E59" s="156"/>
+      <c r="F59" s="156"/>
+      <c r="G59" s="156"/>
+      <c r="H59" s="156"/>
+      <c r="I59" s="156"/>
+      <c r="J59" s="156"/>
+      <c r="K59" s="156"/>
+      <c r="L59" s="156"/>
+      <c r="M59" s="156"/>
+      <c r="N59" s="156"/>
+      <c r="O59" s="156"/>
+      <c r="P59" s="156"/>
+      <c r="Q59" s="156"/>
+      <c r="R59" s="156"/>
+      <c r="S59" s="156"/>
+      <c r="T59" s="156"/>
+      <c r="U59" s="156"/>
+      <c r="V59" s="156"/>
+      <c r="W59" s="156"/>
+      <c r="X59" s="156"/>
+      <c r="Y59" s="156"/>
+      <c r="Z59" s="156"/>
+      <c r="AA59" s="156"/>
+    </row>
+    <row r="60" spans="1:27" ht="15.75">
+      <c r="A60" s="157"/>
+      <c r="B60" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="C60" s="155" t="s">
+        <v>143</v>
+      </c>
+      <c r="D60" s="156"/>
+      <c r="E60" s="156"/>
+      <c r="F60" s="156"/>
+      <c r="G60" s="156"/>
+      <c r="H60" s="156"/>
+      <c r="I60" s="156"/>
+      <c r="J60" s="156"/>
+      <c r="K60" s="156"/>
+      <c r="L60" s="156"/>
+      <c r="M60" s="156"/>
+      <c r="N60" s="156"/>
+      <c r="O60" s="156"/>
+      <c r="P60" s="156"/>
+      <c r="Q60" s="156"/>
+      <c r="R60" s="156"/>
+      <c r="S60" s="156"/>
+      <c r="T60" s="156"/>
+      <c r="U60" s="156"/>
+      <c r="V60" s="156"/>
+      <c r="W60" s="156"/>
+      <c r="X60" s="156"/>
+      <c r="Y60" s="156"/>
+      <c r="Z60" s="156"/>
+      <c r="AA60" s="156"/>
+    </row>
+    <row r="61" spans="1:27" ht="15.75">
+      <c r="A61" s="157"/>
+      <c r="B61" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="C61" s="155" t="s">
+        <v>144</v>
+      </c>
+      <c r="D61" s="156"/>
+      <c r="E61" s="156"/>
+      <c r="F61" s="156"/>
+      <c r="G61" s="156"/>
+      <c r="H61" s="156"/>
+      <c r="I61" s="156"/>
+      <c r="J61" s="156"/>
+      <c r="K61" s="156"/>
+      <c r="L61" s="156"/>
+      <c r="M61" s="156"/>
+      <c r="N61" s="156"/>
+      <c r="O61" s="156"/>
+      <c r="P61" s="156"/>
+      <c r="Q61" s="156"/>
+      <c r="R61" s="156"/>
+      <c r="S61" s="156"/>
+      <c r="T61" s="156"/>
+      <c r="U61" s="156"/>
+      <c r="V61" s="156"/>
+      <c r="W61" s="156"/>
+      <c r="X61" s="156"/>
+      <c r="Y61" s="156"/>
+      <c r="Z61" s="156"/>
+      <c r="AA61" s="156"/>
+    </row>
+    <row r="62" spans="1:27" ht="15.75">
+      <c r="A62" s="157"/>
+      <c r="B62" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="C62" s="155" t="s">
+        <v>145</v>
+      </c>
+      <c r="D62" s="156"/>
+      <c r="E62" s="156"/>
+      <c r="F62" s="156"/>
+      <c r="G62" s="156"/>
+      <c r="H62" s="156"/>
+      <c r="I62" s="156"/>
+      <c r="J62" s="156"/>
+      <c r="K62" s="156"/>
+      <c r="L62" s="156"/>
+      <c r="M62" s="156"/>
+      <c r="N62" s="156"/>
+      <c r="O62" s="156"/>
+      <c r="P62" s="156"/>
+      <c r="Q62" s="156"/>
+      <c r="R62" s="156"/>
+      <c r="S62" s="156"/>
+      <c r="T62" s="156"/>
+      <c r="U62" s="156"/>
+      <c r="V62" s="156"/>
+      <c r="W62" s="156"/>
+      <c r="X62" s="156"/>
+      <c r="Y62" s="156"/>
+      <c r="Z62" s="156"/>
+      <c r="AA62" s="156"/>
+    </row>
+    <row r="63" spans="1:27" ht="15.75">
+      <c r="A63" s="158"/>
+      <c r="B63" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" s="155" t="s">
+        <v>147</v>
+      </c>
+      <c r="D63" s="156"/>
+      <c r="E63" s="156"/>
+      <c r="F63" s="156"/>
+      <c r="G63" s="156"/>
+      <c r="H63" s="156"/>
+      <c r="I63" s="156"/>
+      <c r="J63" s="156"/>
+      <c r="K63" s="156"/>
+      <c r="L63" s="156"/>
+      <c r="M63" s="156"/>
+      <c r="N63" s="156"/>
+      <c r="O63" s="156"/>
+      <c r="P63" s="156"/>
+      <c r="Q63" s="156"/>
+      <c r="R63" s="156"/>
+      <c r="S63" s="156"/>
+      <c r="T63" s="156"/>
+      <c r="U63" s="156"/>
+      <c r="V63" s="156"/>
+      <c r="W63" s="156"/>
+      <c r="X63" s="156"/>
+      <c r="Y63" s="156"/>
+      <c r="Z63" s="156"/>
+      <c r="AA63" s="156"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="A59:A63"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="E2:Q3"/>
+    <mergeCell ref="R2:U2"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A11:A34"/>
     <mergeCell ref="A35:A58"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="E2:Q3"/>
-    <mergeCell ref="R2:U2"/>
-    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12536,6 +13331,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B6F7C28294E8640A8B9BD20A89AFCEF" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="12e02d4d40bc7d3d27cbb6331bb9de43">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="07df7358-ea01-430c-a9ff-b309cd5ad9a1" xmlns:ns3="086ef23d-c247-4f81-a276-5063df7def15" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5f33884f65ae2ddc5ff35eb8b94185e3" ns2:_="" ns3:_="">
     <xsd:import namespace="07df7358-ea01-430c-a9ff-b309cd5ad9a1"/>
@@ -12732,22 +13542,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{727F98F9-AE8E-43E9-AA94-293DD9DBB104}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BCC3382-D9FF-4072-89A8-05135E8C7107}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45A1FF39-FB69-4880-AF9D-C96A3042EAF8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12764,21 +13576,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BCC3382-D9FF-4072-89A8-05135E8C7107}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{727F98F9-AE8E-43E9-AA94-293DD9DBB104}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>